--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$L$235</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$N$235</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -691,17 +691,41 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>¿Quedó incluido al final?</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>columna interna: estado_final</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Por qué se excluyó</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>columna interna: motivo_de_la_exclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Generado el 2026-08-26</t>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Generado el 2026-08-28</t>
         </is>
       </c>
     </row>
@@ -716,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L235"/>
+  <dimension ref="A1:N235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -731,6 +755,8 @@
     <col width="46" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -794,6 +820,16 @@
           <t>Título</t>
         </is>
       </c>
+      <c r="M1" s="8" t="inlineStr">
+        <is>
+          <t>¿Quedó incluido al final?</t>
+        </is>
+      </c>
+      <c r="N1" s="8" t="inlineStr">
+        <is>
+          <t>Por qué se excluyó</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -833,7 +869,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -852,6 +888,12 @@
           <t>Case Report: Arthroscopic "Debridement Antibiotics and Implant Retention" With Local Injection of Personalized</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -891,7 +933,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -910,6 +952,12 @@
           <t xml:space="preserve">Case report: Analysis of phage therapy failure in a patient with a Pseudomonas aeruginosa prosthetic vascular </t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -949,7 +997,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,6 +1016,12 @@
           <t>Refractory Pseudomonas aeruginosa infections treated with phage PASA16: A compassionate use case series.</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1007,7 +1061,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1026,6 +1080,12 @@
           <t>Personalized inhaled bacteriophage therapy for treatment of multidrug-resistant Pseudomonas aeruginosa in cyst</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1065,7 +1125,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1084,6 +1144,12 @@
           <t>Successful adjunctive use of bacteriophage therapy for treatment of multidrug-resistant Pseudomonas aeruginosa</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1123,7 +1189,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1142,6 +1208,12 @@
           <t>Phage Therapy in a Burn Patient Colonized with Extensively Drug-Resistant Pseudomonas aeruginosa Responsible f</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1181,7 +1253,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1200,6 +1272,12 @@
           <t>Adjuvant multisite bacteriophage cocktail administration as salvage treatment in a patient with a multidrug-re</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1239,7 +1317,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1258,6 +1336,12 @@
           <t>Nebulized Phage Therapy for Patients with Cystic Fibrosis with Chronic Pseudomonas aeruginosa Pulmonary Infect</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1297,7 +1381,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1316,6 +1400,12 @@
           <t>Phage therapy with nebulized cocktail BX004-A for chronic Pseudomonas aeruginosa infections in cystic fibrosis</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1355,7 +1445,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1374,6 +1464,12 @@
           <t>Nebulized Bacteriophage Therapy in Cystic Fibrosis Patients With Chronic Pseudomonas Aeruginosa Pulmonary Infe</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1413,7 +1509,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1432,6 +1528,12 @@
           <t>A phase 1b/2a randomized, double-blind, placebo-controlled, multicentre study evaluating nebulized phage thera</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1471,7 +1573,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1486,6 +1588,12 @@
           <t>Nebulized Bacteriophage Therapy in Cystic Fibrosis Patients With Chronic Pseudomonas Aeruginosa Pulmonary Infe</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1525,7 +1633,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1544,6 +1652,12 @@
           <t>A phase 1b/2a randomized, double-blind, placebo-controlled, multicenter study evaluating nebulized phage thera</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1583,7 +1697,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1602,6 +1716,12 @@
           <t>A novel treatment for chronic P. aeruginosa pulmonary infection in CF subjects - A phase 1b/2a randomized, dou</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1641,7 +1761,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1660,6 +1780,12 @@
           <t>WS06.06 Safety and efficacy of a nebulized phage cocktail in cystic fibrosis patients with chronic Pseudomonas</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1699,7 +1825,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1718,6 +1844,12 @@
           <t>Novel nebulized phage cocktail in CF patients with chronic P. aeruginosa pulmonary infection: a Ph1b/2a random</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1757,7 +1889,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1776,6 +1908,12 @@
           <t>Safety and efficacy of nebulized phage in people with cystic fibrosis with chronic Pseudomonas aeruginosa pulm</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1815,7 +1953,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1830,6 +1968,12 @@
           <t>A Phase 1b/2a, Randomized, Double-Blind, Placebo-Controlled, Multicenter Study to Evaluate Nebulized Bacteriop</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1869,7 +2013,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1888,6 +2032,12 @@
           <t>Case Report: Chronic Bacterial Prostatitis Treated With Phage Therapy After Multiple Failed Antibiotic Treatme</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1927,7 +2077,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1946,6 +2096,12 @@
           <t>Personalized bacteriophage therapy to treat pandrug-resistant spinal Pseudomonas aeruginosa infection.</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1985,7 +2141,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2004,6 +2160,12 @@
           <t>A case report of bacteriophage therapy for the treatment of lung infection due to carbapenem-resistant Pseudom</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2043,7 +2205,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2062,6 +2224,12 @@
           <t>Chronic suppression of a multidrug-resistant Pseudomonas aeruginosa in prosthetic joint infection using person</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2101,7 +2269,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2120,6 +2288,12 @@
           <t>Personalized bacteriophage therapy for chronic biliary tract Pseudomonas aeruginosa infections</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2159,7 +2333,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2178,6 +2352,12 @@
           <t>Bacteriophage therapy for empyema caused by carbapenem-resistant Pseudomonas aeruginosa.</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2217,7 +2397,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2236,6 +2416,12 @@
           <t>Combination of phage therapy and cefiderocol to successfully treat Pseudomonas aeruginosa cranial osteomyeliti</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2275,7 +2461,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2294,6 +2480,12 @@
           <t>Use of Phage Cocktail BFC 1.10 in Combination With Ceftazidime-Avibactam in the Treatment of Multidrug-Resista</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2333,7 +2525,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2352,6 +2544,12 @@
           <t>Successful Treatment of a Patient With Chronic Bronchiectasis Using an Induced Native Phage Cocktail: A Case R</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2391,7 +2589,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2410,6 +2608,12 @@
           <t>Bacteriophage therapy in clinical practice: case studies of Pseudomonas aeruginosa infections.</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2449,7 +2653,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2468,6 +2672,12 @@
           <t>Neutralizing antibodies after nebulized phage therapy in cystic fibrosis patients.</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2507,7 +2717,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2526,6 +2736,12 @@
           <t>Adjunctive phage therapy improves antibiotic treatment of ventilator-associated-pneumonia with Pseudomonas aer</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2565,7 +2781,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2580,6 +2796,12 @@
           <t>Evaluation of phage therapy for the treatment of Pseudomonas aeruginosa wound infections in burned patients (P</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2619,7 +2841,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2634,6 +2856,12 @@
           <t xml:space="preserve">Evaluation of Phage Therapy for the Treatment of Escherichia Coli and Pseudomonas Aeruginosa Wound Infections </t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2673,7 +2901,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2692,6 +2920,12 @@
           <t>Efficacy and tolerability of a cocktail of bacteriophages to treat burn wounds infected by Pseudomonas aerugin</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2731,7 +2965,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2746,6 +2980,12 @@
           <t>Individual Patient Expanded Access for AB-PA01, an Investigational Anti-Pseudomonas Aeruginosa Bacteriophage T</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2785,7 +3025,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2804,6 +3044,12 @@
           <t>Bacteriophage Therapy TP-102 in Patients With Diabetic Foot Infection</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2843,7 +3089,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2858,6 +3104,12 @@
           <t>Bacteriophage Therapy TP-102 in Patients With Diabetic Foot Infection</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2897,7 +3149,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2916,6 +3168,12 @@
           <t>Bacteriophage Therapy for Pan-Drug-Resistant Pseudomonas aeruginosa in Two Persons With Cystic Fibrosis.</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2955,7 +3213,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2974,6 +3232,12 @@
           <t>Bacteriophage Therapy in Patients With Prosthetic Joint Infections</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3013,7 +3277,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3028,6 +3292,12 @@
           <t>Bacteriophage Therapy in Patients With Prosthetic Joint Infections</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3067,7 +3337,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3086,6 +3356,12 @@
           <t>Bacteriophage Therapy in Patients With Prosthetic Joint Infections (PJI)</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3125,7 +3401,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3140,6 +3416,12 @@
           <t>Bacteriophage Therapy in Patients With Prosthetic Joint Infections (PJI)</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3179,7 +3461,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3198,6 +3480,12 @@
           <t>Personalized aerosolised bacteriophage treatment of a chronic lung infection due to multidrug-resistant Pseudo</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3237,7 +3525,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3256,6 +3544,12 @@
           <t>A feasibility study for personalized phage therapy against drug-resistant bacteria in Japan.</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3295,7 +3589,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3314,6 +3608,12 @@
           <t>Randomized double-blind study on safety and tolerability of TP-102 phage cocktail in patients with infected an</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3353,7 +3653,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3372,6 +3672,12 @@
           <t>Bacteriophage Therapy TP-102 in Diabetic Foot Ulcers</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3411,7 +3717,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3426,6 +3732,12 @@
           <t>Bacteriophage Therapy TP-102 in Diabetic Foot Ulcers</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3465,7 +3777,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3484,6 +3796,12 @@
           <t>Assessing the safety of TP-102 bacteriophage treatment in the management of diabetic foot infections</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3523,7 +3841,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3542,6 +3860,12 @@
           <t>Clearance of hypermutator XDR Pseudomonas osteomyelitis and hardware infection with adjunctive bacteriophage t</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3581,7 +3905,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3600,6 +3924,12 @@
           <t>Harnessing bacteriophages to combat antibiotic-resistant chronic postoperative infections: A promising case se</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3639,7 +3969,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3658,6 +3988,12 @@
           <t>Refractory Pseudomonas Bacteremia in a 2-Year-Old Sterilized by Bacteriophage Therapy.</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3697,7 +4033,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3716,6 +4052,12 @@
           <t>Bacteriophage Therapy of Ventilator-associated Pneumonia and Empyema Caused by Pseudomonas aeruginosa.</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3755,7 +4097,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3774,6 +4116,12 @@
           <t>Lessons Learned From the First 10 Consecutive Cases of Intravenous Bacteriophage Therapy to Treat Multidrug-Re</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3813,7 +4161,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3828,6 +4176,12 @@
           <t>A Phase 1b/2 Trial of the Safety and Microbiological Activity of Bacteriophage Therapy in Cystic Fibrosis Subj</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3867,7 +4221,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3886,6 +4240,12 @@
           <t>A Phase 1b/2 Trial of the Safety and Microbiological Activity of Bacteriophage Therapy in Cystic Fibrosis Subj</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3925,7 +4285,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3944,6 +4304,12 @@
           <t>Safety and microbiological activity of phage therapy in persons with cystic fibrosis colonized with Pseudomona</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3983,7 +4349,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4002,6 +4368,12 @@
           <t>A Randomized Controlled Trial of Bacteriophage Cocktail Therapy for Multidrug-Resistant Gram-Negative Ventilat</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4041,7 +4413,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4060,6 +4432,12 @@
           <t>Pan-Resistant Pseudomonas aeruginosa Septic Shock in a Critically Ill Patient: A Case Report.</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4099,7 +4477,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4118,6 +4496,12 @@
           <t>Phage Therapy Experience at the Eliava Phage Therapy Center: Three Cases of Bacterial Persistence.</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4157,7 +4541,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4176,6 +4560,12 @@
           <t>Adaptive Phage Therapy for the Prevention of Recurrent Nosocomial Pneumonia: Novel Protocol Description and Ca</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4215,7 +4605,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4234,6 +4624,12 @@
           <t>Refractory Pseudomonas aeruginosa Bronchopulmonary Infection After Lung Transplantation for Common Variable Im</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4273,7 +4669,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4292,6 +4688,12 @@
           <t>Optimized preparation pipeline for emergency phage therapy against Pseudomonas aeruginosa at Yale University.</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4331,7 +4733,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4350,6 +4752,12 @@
           <t>Phage therapy of perinephric abscess in kidney transplantation recipients caused by drug-resistant Pseudomonas</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4389,7 +4797,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4408,6 +4816,12 @@
           <t>Calciphylaxis complicated by NDM-1-producing Pseudomonas aeruginosa: first experience with cefepime-zidebactam</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4447,7 +4861,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4466,6 +4880,12 @@
           <t>Successful Bacteriophage Treatment of a Recalcitrant Intra-Abdominal Infection Caused by Multidrug-Resistant P</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4505,7 +4925,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4524,6 +4944,12 @@
           <t>Concept of individualized medicine based on personalized phage therapy for intensive care unit patients suffer</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4563,7 +4989,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4582,6 +5008,12 @@
           <t>Use of bacteriophages in the treatment of colistin-only-sensitive Pseudomonas aeruginosa septicaemia in a pati</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4621,7 +5053,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4640,6 +5072,12 @@
           <t>Bacteriophages as Adjuvant to Antibiotics for the Treatment of Periprosthetic Joint Infection Caused by Multid</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4679,7 +5117,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4698,6 +5136,12 @@
           <t>Application of Phage Therapy in a Case of a Chronic Hip-Prosthetic Joint Infection due to Pseudomonas aerugino</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4737,7 +5181,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4756,6 +5200,12 @@
           <t>Development of Host Immune Response to Bacteriophage in a Lung Transplant Recipient on Adjunctive Phage Therap</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4795,7 +5245,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4814,6 +5264,12 @@
           <t>Access to phage therapy at Hospices Civils de Lyon in 2022: Implementation of the PHAGEinLYON Clinic programme</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4853,7 +5309,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4868,6 +5324,12 @@
           <t>Avis-PHAGEinLYON Clinic</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4907,7 +5369,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4926,6 +5388,12 @@
           <t>Case report: Local bacteriophage therapy for fracture-related infection with polymicrobial multi-resistant bac</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4965,7 +5433,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4984,6 +5452,12 @@
           <t>Cystic Fibrosis Bacteriophage Study at Yale (CYPHY)</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5023,7 +5497,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5042,6 +5516,12 @@
           <t>CYstic Fibrosis bacterioPHage study at Yale (CYPHY)</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5081,7 +5561,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5100,6 +5580,12 @@
           <t>CYstic Fibrosis bacterioPHage study at Yale (CYPHY)</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5139,7 +5625,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5158,6 +5644,12 @@
           <t>CYstic Fibrosis bacterioPHage Study at Yale (CYPHY)</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5197,7 +5689,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5212,6 +5704,12 @@
           <t>CYstic Fibrosis bacterioPHage Study at Yale (CYPHY)</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5251,7 +5749,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5270,6 +5768,12 @@
           <t>Phage-Antibiotic Combination Therapy against Recurrent Pseudomonas Septicaemia in a Patient with an Arterial S</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5309,7 +5813,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5328,6 +5832,12 @@
           <t>Bacteriophage Therapy for Chronic Mastoiditis.</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5367,7 +5877,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5386,6 +5896,12 @@
           <t>Bacteriophage therapy in women with chronic recurrent cystitis caused by multidrug-resistant bacteria: A prosp</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5425,7 +5941,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5444,6 +5960,12 @@
           <t>Bacteriophages in Addition to Antibiotics for the Treatment of Patients with Infective Endocarditis</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5483,7 +6005,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5498,6 +6020,12 @@
           <t>Bacteriophages in Addition to Antibiotics for the Treatment of Patients With Infective Endocarditis</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5537,7 +6065,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5556,6 +6084,12 @@
           <t>Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Bentall Infection.</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5595,7 +6129,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5614,6 +6148,12 @@
           <t xml:space="preserve">Resolution of acute rejection in a bilateral double-lung transplanted cystic fibrosis patient following phage </t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5653,7 +6193,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5672,6 +6212,12 @@
           <t>Anti-phage antibody response in phage therapy against healthcare-associated infections (HAIs)</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5711,7 +6257,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5730,6 +6276,12 @@
           <t xml:space="preserve">Clinical Indications and Compassionate Use of Phage Therapy: Personal Experience and Literature Review with a </t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5769,7 +6321,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5788,6 +6340,12 @@
           <t>Early clinical experience of bacteriophage therapy in 3 lung transplant recipients.</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5827,7 +6385,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5846,6 +6404,12 @@
           <t>Bacteriophage-antibiotic combination therapy against extensively drug-resistant Pseudomonas aeruginosa infecti</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5885,7 +6449,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5904,6 +6468,12 @@
           <t xml:space="preserve">Single-arm, open-labelled, safety and tolerability of intrabronchial and nebulised bacteriophage treatment in </t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5943,7 +6513,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5962,6 +6532,12 @@
           <t>Adjunctive bacteriophage therapy for refractory/resistant Pseudomonas aeruginosa infections: Bottlenecks and p</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6001,7 +6577,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6024,6 +6600,12 @@
           <t>Successful phage therapy in a patient with prosthetic joint infection</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6063,7 +6645,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6082,6 +6664,12 @@
           <t>Phage Therapy for the Prevention and Treatment of Wound Infections in Burned Patients</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6121,7 +6709,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6136,6 +6724,12 @@
           <t>Phage Therapy for the Prevention and Treatment of Wound Infections in Burned Patients</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6175,7 +6769,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6194,6 +6788,12 @@
           <t>A three part randomized, double-blind, placebo-controlled, parallel group SAD and MD clinical study to evaluat</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6233,7 +6833,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6252,6 +6852,12 @@
           <t>A two part, randomized, double-blind, placebo-controlled, parallel group SAD and MD clinical study to evaluate</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6291,7 +6897,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6310,6 +6916,12 @@
           <t>Compassionate Use of Bacteriophages for Failed Persistent Infections During the First 5 Years of the Israeli P</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6349,7 +6961,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6368,6 +6980,12 @@
           <t>Investigating phage therapy in the prevention of ventilator-induced bacterial pneumonia in patients admitted t</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6407,7 +7025,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6426,6 +7044,12 @@
           <t>Proof of Concept Study to Assess Safety and Efficacy of Phage Therapy in Hip or Knee Prosthetic Joint Infectio</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6465,7 +7089,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6480,6 +7104,12 @@
           <t>Proof of Concept Study to Assess Safety and Efficacy of Phage Therapy in Hip or Knee Prosthetic Joint Infectio</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6519,7 +7149,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6538,6 +7168,12 @@
           <t>Bacteriophage Therapy of Chronic Nonhealing Wound: Clinical Study.</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6577,7 +7213,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6596,6 +7232,12 @@
           <t>Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surgery.</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6635,7 +7277,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6658,6 +7300,12 @@
           <t>Phage therapy in antibiotic resistant pneumonia: Immunomodulation or redistribution?</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6697,7 +7345,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6716,6 +7364,12 @@
           <t>Experience Using Adjuvant Bacteriophage Therapy for the Treatment of 10 Recalcitrant Periprosthetic Joint Infe</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6755,7 +7409,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6774,6 +7428,12 @@
           <t>Pseudomonas aeruginosa ventricular assist device infections: findings from ineffective phage therapies in five</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6813,7 +7473,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6832,6 +7492,12 @@
           <t>Efficacy of Bacteriophage Therapy in the Treatment of Diabetic Foot Ulcers: a Pilot Study from South India</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6871,7 +7537,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6890,6 +7556,12 @@
           <t>Bacteriophage Therapy as a Potential Management Option for Surgical Wound Infections</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6929,7 +7601,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6948,6 +7620,12 @@
           <t>Bacteriophage therapy as a treatment option for transplant infections.</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6987,7 +7665,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7002,6 +7680,12 @@
           <t>Ph 1/2 Study Evaluating Safety and Tolerability of Inhaled AP-PA02 in Subjects With Chronic Pseudomonas Aerugi</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7041,7 +7725,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7060,6 +7744,12 @@
           <t>Ph 1/2 Study Evaluating Safety and Tolerability of Inhaled AP-PA02 in Subjects With Chronic Pseudomonas Aerugi</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7099,7 +7789,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7118,6 +7808,12 @@
           <t xml:space="preserve">Bacteriophage Therapy for Difficult-to-Treat Infections: The Implementation of a Multidisciplinary Phage Task </t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7157,7 +7853,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7172,6 +7868,12 @@
           <t xml:space="preserve">Bacteriophage Therapy for Difficult-to-treat Infections: the Implementation of a Multidisciplinary Phage Task </t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7211,7 +7913,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7230,6 +7932,12 @@
           <t>Study to Evaluate the Safety, Phage Kinetics, and Efficacy of Inhaled AP-PA02 in Subjects With Non-Cystic Fibr</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7269,7 +7977,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7284,6 +7992,12 @@
           <t>Study to Evaluate the Safety, Phage Kinetics, and Efficacy of Inhaled AP-PA02 in Subjects With Non-Cystic Fibr</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7323,7 +8037,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7342,6 +8056,12 @@
           <t>First-in-human application of double-stranded RNA bacteriophage in the treatment of pulmonary Pseudomonas aeru</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7381,7 +8101,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7400,6 +8120,12 @@
           <t>Inhalation phage therapy as a new approach to preventing secondary bacterial pneumonia in patients with modera</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7439,7 +8165,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7458,6 +8184,12 @@
           <t>Inhalation phage therapy as a new approach to preventing secondary bacterial pneumonia in patients with modera</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7497,7 +8229,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7512,6 +8244,12 @@
           <t>PHAGEinLYON Clinic Cohort Study: a Descriptive Study of Severe Infections Treated With Phage Therapy at the HC</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7551,7 +8289,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7570,6 +8308,12 @@
           <t>Case report: Personalized triple phage-antibiotic combination therapy to rescue necrotizing fasciitis caused b</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7609,7 +8353,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7628,6 +8372,12 @@
           <t>Analysis of Pro- and Anti-Inflammatory Gene Response Patterns in Patients Receiving Phage Therapy.</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7667,7 +8417,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7690,6 +8440,12 @@
           <t>Phage therapy analysis of effectiveness in comorbid patients with wounds and surgical infections of various et</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7729,7 +8485,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7748,6 +8504,12 @@
           <t>Pharmacodynamic individualization of phage therapy against a KPC-5-producing Pseudomonas aeruginosa.</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7787,7 +8549,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7806,6 +8568,12 @@
           <t>Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas aeruginosa mediastinitis and vascu</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7845,7 +8613,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7864,6 +8632,12 @@
           <t>Bacterial lysis, autophagy and innate immune responses during adjunctive phage therapy in a child.</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7903,7 +8677,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7922,6 +8696,12 @@
           <t>Low immunogenicity of intravesical phage therapy for urogenitary tract infections</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7961,7 +8741,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7980,6 +8760,12 @@
           <t>Phage Therapy for the Prevention and Treatment of Pressure Ulcers</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8019,7 +8805,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8034,6 +8820,12 @@
           <t>Phage Therapy for the Prevention and Treatment of Pressure Ulcers.</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8073,7 +8865,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8092,6 +8884,12 @@
           <t>Bacteriophage therapy as a treatment option for complex cardiovascular implant infection: The German Heart Cen</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8131,7 +8929,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8150,6 +8948,12 @@
           <t>Evaluation of safety and effectiveness of a nebulised phage cocktail in patients with chronic rhinosinusitis (</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8189,7 +8993,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8208,6 +9012,12 @@
           <t xml:space="preserve">The Efficacy of Inhaled Phage Cocktail to Prevent Ventilator-Associated Pneumonia in Children: A Double-Blind </t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8247,7 +9057,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8266,6 +9076,12 @@
           <t xml:space="preserve">The Efficacy of Inhaled Phage Cocktail to Prevent Ventilator-Associated Pneumonia in Children: a Double-Blind </t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8305,7 +9121,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8324,6 +9140,12 @@
           <t>A randomized, double-blind clinical trial of phage nebulized inhalation for the treatment of respiratory tract</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8363,7 +9185,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8386,6 +9208,12 @@
           <t>Phage therapy of purulent wounds: comparative clinical cytomorphological and microbiological analysis of effec</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8425,7 +9253,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8440,6 +9268,12 @@
           <t>Bacteriophage Clinical Trial for Periprosthetic Joint Infection of Multidrug Resistant Pseudomonas Aeruginosa</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8479,7 +9313,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8498,6 +9332,12 @@
           <t>Innovations for the treatment of a complex bone and joint infection due to XDR Pseudomonas aeruginosa includin</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8537,7 +9377,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8556,6 +9396,12 @@
           <t>Phage treatment of an aortic graft infected with Pseudomonas aeruginosa.</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8595,7 +9441,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8610,6 +9456,12 @@
           <t>Bacteriophage Therapy in First Time Chronic Prosthetic Joint Infections</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8649,7 +9501,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8668,6 +9520,12 @@
           <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: a multicentre, multinational, retrospec</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8707,7 +9565,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8722,6 +9580,12 @@
           <t>Bacteriophage Therapy of Difficult-to-treat Infections</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8761,7 +9625,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8780,6 +9644,12 @@
           <t>Successful Use of Phage and Antibiotics Therapy for the Eradication of Two Bacterial Pathogens from the Respir</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8819,7 +9689,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8838,6 +9708,12 @@
           <t>Bacteriophage Cocktail Therapy for Multidrug-Resistant Gram-Negative Ventilator-Associated Pneumonia</t>
         </is>
       </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8877,7 +9753,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8892,6 +9768,12 @@
           <t>Bacteriophage Cocktail Therapy for Multidrug-Resistant Gram-Negative Ventilator-Associated Pneumonia</t>
         </is>
       </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8931,7 +9813,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8946,6 +9828,12 @@
           <t>Safety of Combined Intravenous Antibiotic and Bacteriophage Therapy in Adults With Cystic Fibrosis and Antibio</t>
         </is>
       </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8985,7 +9873,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9004,6 +9892,12 @@
           <t>Randomized Controlled Study on the Safety and Efficacy of Phage Cocktail in the Treatment of Multidrug-Resista</t>
         </is>
       </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9043,7 +9937,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9058,6 +9952,12 @@
           <t>Randomized Controlled Study on the Safety and Efficacy of Phage Cocktail in the Treatment of Multidrug-Resista</t>
         </is>
       </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9097,7 +9997,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9112,6 +10012,12 @@
           <t>Personalized Phage Treatment in Covid-19 Patients With Bacterial Co-Infections Microbials for Pneumonia or Bac</t>
         </is>
       </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9151,7 +10057,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9170,6 +10076,12 @@
           <t>Antiphage activity of sera during phage therapy in relation to its outcome.</t>
         </is>
       </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9209,7 +10121,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9228,6 +10140,12 @@
           <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Identified.</t>
         </is>
       </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9267,7 +10185,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9286,6 +10204,12 @@
           <t>Anti-phage serum antibody responses and the outcome of phage therapy.</t>
         </is>
       </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9325,7 +10249,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9344,6 +10268,12 @@
           <t>Intravesical bacteriophages for treating urinary tract infections in patients undergoing transurethral resecti</t>
         </is>
       </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9383,7 +10313,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9402,6 +10332,12 @@
           <t>Bacteriophages for treating urinary tract infections in patients undergoing transurethral resection of the pro</t>
         </is>
       </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9441,7 +10377,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9456,6 +10392,12 @@
           <t>Bacteriophages for Treating Urinary Tract Infections in Patients Undergoing Transurethral Resection of the Pro</t>
         </is>
       </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9495,7 +10437,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9514,6 +10456,12 @@
           <t>Bacteriophages for Treating Urinary Tract Infections in Patients Undergoing Transurethral Resection of the Pro</t>
         </is>
       </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9553,7 +10501,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9572,6 +10520,12 @@
           <t>Intravesical bacteriophages for treating urinary tract infections in patients undergoing transurethral resecti</t>
         </is>
       </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9611,7 +10565,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9630,6 +10584,12 @@
           <t>Phage therapy for prevention of secondary bacterial pneumonia in COVID-19</t>
         </is>
       </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9669,7 +10629,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9688,6 +10648,12 @@
           <t>Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report</t>
         </is>
       </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9727,7 +10693,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9746,6 +10712,12 @@
           <t xml:space="preserve">Standardised treatment and monitoring protocol to assess safety and tolerability of bacteriophage therapy for </t>
         </is>
       </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9785,7 +10757,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9806,6 +10778,16 @@
       <c r="L158" t="inlineStr">
         <is>
           <t>INFLUENCE OF INHALED BACTERIOPHAGE THERAPY ON ORAL MUCOSAL IMMUNITY IN CHILDREN WITH ACUTE TONSILLITIS</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Informe no redactado en ingles ni en espanol (criterio de idioma, enmienda 2026-08-11); comprobado sobre el TEXTO COMPLETO en la web del editor: la revista rotula el cuerpo como Full Text (RUSSIAN) y solo el resumen esta en ingles. Los metadatos declaraban ingles.</t>
         </is>
       </c>
     </row>
@@ -9847,7 +10829,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9866,6 +10848,12 @@
           <t>Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-Resistant Pseudomonas aeruginosa Lef</t>
         </is>
       </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9905,7 +10893,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9924,6 +10912,12 @@
           <t>Application of bacteriophage therapy in the treatment of children with acute tonsillitis</t>
         </is>
       </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9963,7 +10957,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9982,6 +10976,12 @@
           <t>Application of bacteriophage therapy in the treatment of children with acute tonsillitis</t>
         </is>
       </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10021,7 +11021,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10040,6 +11040,12 @@
           <t>Phage Therapy for Orthopaedic Infections: The First Three Cases from the United Kingdom</t>
         </is>
       </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10079,7 +11085,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10098,6 +11104,12 @@
           <t>Prolonged disease remission of the chronic immunological skin disorder hidradenitis suppurativa with adjunctiv</t>
         </is>
       </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -10137,7 +11149,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10156,6 +11168,12 @@
           <t>Results of TOR001: An open-label single patient study using targeted bacteriophage therapy for the treatment o</t>
         </is>
       </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10195,7 +11213,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10214,6 +11232,12 @@
           <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Management of Pressure Ulcers and Its Co</t>
         </is>
       </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10253,7 +11277,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10272,6 +11296,12 @@
           <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Management of Pressure Ulcers and Its Co</t>
         </is>
       </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10311,7 +11341,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10330,6 +11360,12 @@
           <t>Phage therapy for the treatment for urinary tract infection: results of in-vitro screenings and in-vivo applic</t>
         </is>
       </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10369,7 +11405,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10388,6 +11424,12 @@
           <t>Adapted Bacteriophages for Treating Urinary Tract Infections.</t>
         </is>
       </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10427,7 +11469,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10446,6 +11488,12 @@
           <t>Adapted bacteriophages for treating urinary tract infections</t>
         </is>
       </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10485,7 +11533,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10504,6 +11552,12 @@
           <t>The Potential Innovative Use of Bacteriophages Within the DAC® Hydrogel to Treat Patients With Knee Megaprosth</t>
         </is>
       </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10543,7 +11597,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10562,6 +11616,12 @@
           <t>"Debridement PhagE AnTibiotics for PJI"</t>
         </is>
       </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10601,7 +11661,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10616,6 +11676,12 @@
           <t>"Debridement PhagE AnTibiotics for PJI"</t>
         </is>
       </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10655,7 +11721,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10670,6 +11736,12 @@
           <t>PHRC-N/2015/AS-01 - Comparison of the efficacy of standard treatment associated with phage therapy versus stan</t>
         </is>
       </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10709,7 +11781,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10728,6 +11800,12 @@
           <t>Novel bacteriophage therapy for treatment of left ventricular assist device infection.</t>
         </is>
       </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10767,7 +11845,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10782,6 +11860,12 @@
           <t>Bacteriophage Therapy in Tonsillitis</t>
         </is>
       </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10821,7 +11905,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10840,6 +11924,12 @@
           <t>Chronic non healing ulcer and bacteriophage therapy</t>
         </is>
       </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10879,7 +11969,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -10898,6 +11988,12 @@
           <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized Phage Therapy: Production, Char</t>
         </is>
       </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10937,7 +12033,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -10960,6 +12056,12 @@
           <t>Complex surgical treatment of recurrent post-injection abscess in a patient with systemic autoimmune disease</t>
         </is>
       </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10999,7 +12101,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11014,6 +12116,12 @@
           <t>Phage Therapy for the Treatment of Urinary Tract Infection</t>
         </is>
       </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11053,7 +12161,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11072,6 +12180,12 @@
           <t>Study to phages for prevention and treatment of difficult-to-treat resistant Pseudomonas aeruginosa infection</t>
         </is>
       </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11111,7 +12225,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11126,6 +12240,12 @@
           <t>Use of Phage Therapy for Treatment of a Periprosthetic Joint Infection</t>
         </is>
       </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11165,7 +12285,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11184,6 +12304,12 @@
           <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages</t>
         </is>
       </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11223,7 +12349,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11238,6 +12364,12 @@
           <t>Evaluation of Safety and Efficacy of Phage Therapy for Drug-resistant Bacterial Infections: An Exploratory, Pr</t>
         </is>
       </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11277,7 +12409,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11296,6 +12428,12 @@
           <t>Phase 1/2a to Assess the Safety and Tolerability of TP-122A for the Treatment of Ventilator-Associated Pneumon</t>
         </is>
       </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11335,7 +12473,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11350,6 +12488,12 @@
           <t>Phase 1/2a to Assess the Safety and Tolerability of TP-122A for the Treatment of Ventilator-Associated Pneumon</t>
         </is>
       </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11389,7 +12533,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11408,6 +12552,12 @@
           <t>Efficacy and safety of bacteriophage in treating severe drug-resistant lower respiratory tract infections in c</t>
         </is>
       </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11447,7 +12597,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11466,6 +12616,12 @@
           <t>Phase 2b Randomized, Double-Blind Study with Phage for CF Subjects with Pseudomonas Lung Infection</t>
         </is>
       </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11505,7 +12661,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11524,6 +12680,12 @@
           <t>A Randomized, Placebo-controlled, Double-blind Clinical Trial of Bacteriophage Cocktails in Chronic Wound Infe</t>
         </is>
       </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11563,7 +12725,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -11578,6 +12740,12 @@
           <t>Bacteriophage Effects on Pseudomonas Aeruginosa</t>
         </is>
       </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11617,7 +12785,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -11636,6 +12804,12 @@
           <t>Bacteriophage-Enriched Galenic for Intrapericardial Ventricular Assist Device Infection</t>
         </is>
       </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11675,7 +12849,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -11694,6 +12868,12 @@
           <t>A Randomized Controlled Trial on the Safety and Efficacy of Phage Cocktail Therapy for Multidrug-Resistant Bac</t>
         </is>
       </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11733,7 +12913,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -11748,6 +12928,12 @@
           <t>MP101 in Adults With Acute Pseudomonas Aeruginosa Pneumonia</t>
         </is>
       </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11787,7 +12973,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -11806,6 +12992,12 @@
           <t>Phase 1 Study of MP101 in Adults With Acute Pseudomonas aeruginosa Pneumonia</t>
         </is>
       </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11845,7 +13037,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -11864,6 +13056,12 @@
           <t>Bacteriophage Application for Difficult-to-treat Musculoskeletal Infections: Development of a Standardized Mul</t>
         </is>
       </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11903,7 +13101,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -11922,6 +13120,12 @@
           <t>Use of Customized Bacteriophages in the Treatment of Chronic Nonhealing Wounds: A Prospective Study.</t>
         </is>
       </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11961,7 +13165,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -11980,6 +13184,12 @@
           <t>Biological Therapy on Infected Traumatic Wounds: A Case-Control Study.</t>
         </is>
       </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -12019,7 +13229,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12038,6 +13248,12 @@
           <t>Safety and tolerability of bronchoscopic and nebulised administration of bacteriophage.</t>
         </is>
       </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -12077,7 +13293,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12096,6 +13312,12 @@
           <t>Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aortic aneurysm</t>
         </is>
       </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12135,7 +13357,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12154,6 +13376,12 @@
           <t>Yiqi Huoxue Jiedu Formula Combined With Bacteriophages in the Treatment of Severe Pneumonia</t>
         </is>
       </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12193,7 +13421,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12208,6 +13436,12 @@
           <t>Yiqi Huoxue Jiedu Formula Combined With Bacteriophages in the Treatment of Severe Pneumonia</t>
         </is>
       </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12247,7 +13481,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12266,6 +13500,12 @@
           <t>Study to assess the Safety and Efficacy of Bacteriophage in the treatment of Diabetic foot infection</t>
         </is>
       </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12305,7 +13545,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12324,6 +13564,12 @@
           <t>Use of bacteriophages in the treatment of infected wounds in patients who have allergy to antibiotics</t>
         </is>
       </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12363,7 +13609,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12382,6 +13628,12 @@
           <t>A randomized, double-blind, placebo- -controlled study to investigate the use of bacteriophages in patients wi</t>
         </is>
       </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12421,7 +13673,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12440,6 +13692,12 @@
           <t xml:space="preserve">CLINICAL AND LABORATORY JUSTIFICATION FOR USE OF POLYVALENT BACTERIOPHAGE IN TECHNIQUE OF DELAYED PRESCRIBING </t>
         </is>
       </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12479,7 +13737,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12498,6 +13756,12 @@
           <t xml:space="preserve">Short-Term Outcomes of Phage-Antibiotic Combination Treatment in Adult Patients with Periprosthetic Hip Joint </t>
         </is>
       </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12537,7 +13801,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -12552,6 +13816,12 @@
           <t>Phase 1b/2a Randomized Double-blind Study to Investigate Safety Tolerability PK PD Preliminary Efficacy of Ora</t>
         </is>
       </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12591,7 +13861,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -12610,6 +13880,12 @@
           <t>Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection</t>
         </is>
       </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12649,7 +13925,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -12668,6 +13944,12 @@
           <t>The management of sternal mediastinitis in heart and lung transplant patients: An 8-year experience and applic</t>
         </is>
       </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12707,7 +13989,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -12722,6 +14004,12 @@
           <t>Phage4Cure-001 - A three part randomized, double-blind, placebo-controlled, parallel group SAD and MD clinical</t>
         </is>
       </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12761,7 +14049,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -12776,6 +14064,12 @@
           <t xml:space="preserve">Phage4Cure-001 - A two part, randomized, double-blind, placebo-controlled, parallel group SAD and MD clinical </t>
         </is>
       </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12815,7 +14109,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -12834,6 +14128,12 @@
           <t>Potential treatment method of recurrent urinary tract infection in postmenopausal kidney transplant recipients</t>
         </is>
       </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12873,7 +14173,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -12892,6 +14192,12 @@
           <t>Phage-Antibiotic Combination Therapy for Multidrug-Resistant Infections: a Prospective Study</t>
         </is>
       </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12931,7 +14237,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -12946,6 +14252,12 @@
           <t>BMX-04-002 - A Phase 2b, Randomized, Double-Blind, Placebo-Controlled, Multicenter Study to Evaluate Nebulized</t>
         </is>
       </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12985,7 +14297,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13000,6 +14312,12 @@
           <t>The Effect of Supraglottic and Oropharyngeal Decontamination on the Incidence of Ventilator-associated Pneumon</t>
         </is>
       </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -13039,7 +14357,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13058,6 +14376,12 @@
           <t>The Effect of Supraglottic and Oropharyngeal Decontamination on the Incidence of Ventilator-associated Pneumon</t>
         </is>
       </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13097,7 +14421,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13116,6 +14440,12 @@
           <t>Successful use of a phage endolysin for treatment of chronic pelvic pain syndrome/chronic bacterial prostatiti</t>
         </is>
       </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13155,7 +14485,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13174,6 +14504,12 @@
           <t>Study With Phage for CF Subjects With Pseudomonas Lung Infection</t>
         </is>
       </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13213,7 +14549,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13228,6 +14564,12 @@
           <t>Study With Phage for CF Subjects With Pseudomonas Lung Infection</t>
         </is>
       </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13267,7 +14609,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13286,6 +14628,12 @@
           <t>The effect of Bacteriophage on Diabetic foot Ulcers</t>
         </is>
       </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13325,7 +14673,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13340,6 +14688,12 @@
           <t>A Prospective, Randomized, Double-Blind Controlled Study of WPP-201 for the Safety and Efficacy of Treatment o</t>
         </is>
       </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13379,7 +14733,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13394,6 +14748,12 @@
           <t>Antibacterial Treatment Against Diarrhea in Oral Rehydration Solution</t>
         </is>
       </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13433,7 +14793,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -13452,6 +14812,12 @@
           <t>Beneficios obtenidos con el empleo de bacteriófagos en el tratamiento de infecciones crónicas</t>
         </is>
       </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13491,7 +14857,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -13510,6 +14876,12 @@
           <t>Successful bacteriophage treatment of infection involving cardiac implantable electronic device and aortic gra</t>
         </is>
       </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13549,7 +14921,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -13568,6 +14940,12 @@
           <t>Treatment of chronic left ventricular assist device infection with local application of bacteriophages.</t>
         </is>
       </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13607,7 +14985,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -13622,6 +15000,12 @@
           <t>Phage Safety Retrospective Cohort Study</t>
         </is>
       </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13661,7 +15045,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -13676,6 +15060,12 @@
           <t xml:space="preserve">A Study Investigating the Safety, Recovery, and Pharmacodynamics of Multiple Oral Administrations of SNIPR001 </t>
         </is>
       </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13715,7 +15105,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -13730,6 +15120,12 @@
           <t>BActeriophages To Treat Liver Disease Eliminating Harmful Bacteria (BATTLE)</t>
         </is>
       </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13769,7 +15165,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -13788,6 +15184,12 @@
           <t>Local Treatment of Driveline Infection with Bacteriophages</t>
         </is>
       </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13827,7 +15229,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -13842,6 +15244,12 @@
           <t>Mayo Clinic Phage Program Biobank</t>
         </is>
       </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13881,7 +15289,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -13896,6 +15304,12 @@
           <t>Phage Safety Cohort Study</t>
         </is>
       </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13935,7 +15349,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -13950,6 +15364,12 @@
           <t>Clinical Trial to Demonstrate the Safety and Efficacy of DUOFAG®</t>
         </is>
       </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13989,7 +15409,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14004,6 +15424,12 @@
           <t>Treatment Chronic UTI Post Kidney Transplant</t>
         </is>
       </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -14043,7 +15469,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14062,6 +15488,12 @@
           <t>Evaluate the effect of bacteriophage in pressure ulcers</t>
         </is>
       </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14101,7 +15533,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14116,6 +15548,12 @@
           <t>Biomarkers of Phage Treatment Response in NTM and Other Infections</t>
         </is>
       </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14155,7 +15593,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>ADMITIDO</t>
+          <t>admitido</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14178,9 +15616,15 @@
           <t>Bacteriophages in complex treatment of septic diseases of the hand</t>
         </is>
       </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L235"/>
+  <autoFilter ref="A1:N235"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -725,7 +725,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-28</t>
+          <t>Generado el 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -725,7 +725,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-31</t>
+          <t>Generado el 2026-09-01</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -2546,10 +2546,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>INT: Inducen-Res(R): solucion oral "imprinted with the induction signatures" para inducir los fagos nativos del propio paciente; no se administra ningun fago. Ademas sin diagnostico confirmado.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2738,10 +2742,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>LAB: Modelo murino de neumonia asociada a ventilacion.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4178,10 +4186,14 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>PRO: STUDY PROTOCOL en Trials (2022). 99 ocurrencias de "will be".</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4242,10 +4254,14 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>PRO: STUDY PROTOCOL en Trials (2022). 99 ocurrencias de "will be".</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4306,10 +4322,14 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>PRO: STUDY PROTOCOL en Trials (2022). 99 ocurrencias de "will be".</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4434,10 +4454,14 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>OFF: Caso de shock septico por P. aeruginosa PDR donde el fago solo se menciona como opcion no disponible.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4690,10 +4714,14 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>LAB: Articulo de metodos: canal de preparacion de fagos en el laboratorio.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5454,10 +5482,14 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>PRO: Documento de protocolo CYPHY, Yale, version 11. 223 ocurrencias de "will be".</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5518,10 +5550,14 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>PRO: Documento de protocolo CYPHY, Yale, version 11. 223 ocurrencias de "will be".</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5582,10 +5618,14 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>PRO: Documento de protocolo CYPHY, Yale, version 11. 223 ocurrencias de "will be".</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5646,10 +5686,14 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>PRO: Documento de protocolo CYPHY, Yale, version 11. 223 ocurrencias de "will be".</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5706,10 +5750,14 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>PRO: Documento de protocolo CYPHY, Yale, version 11. 223 ocurrencias de "will be".</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6278,10 +6326,14 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>REV: Pieza de opinion con revision de la literatura y experiencia propia.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7366,10 +7418,14 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>ORG: Cero menciones. Artroplastias infectadas por Staphylococcus.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7810,10 +7866,14 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>PRO: PHAGEFORCE Study Protocol. P. aeruginosa solo aparece en la introduccion.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7870,10 +7930,14 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>PRO: PHAGEFORCE Study Protocol. P. aeruginosa solo aparece en la introduccion.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8122,10 +8186,14 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>ORG: Cepa de referencia ATCC 27853 usada para fabricar el coctel; pacientes de COVID-19.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8186,10 +8254,14 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>ORG: Cepa de referencia ATCC 27853 usada para fabricar el coctel; pacientes de COVID-19.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8506,10 +8578,14 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>LAB: Modelo in vitro: time-kill de 24 h y hollow fibre de 7 dias.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9014,10 +9090,14 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>ORG: Ninos ventilados; los criterios excluian neumonia bacteriana; cultivos negativos.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9078,10 +9158,14 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>ORG: Ninos ventilados; los criterios excluian neumonia bacteriana; cultivos negativos.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10714,10 +10798,14 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>PRO: STAMP study protocol, abierto de un solo brazo. 80 ocurrencias de "will be".</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10914,10 +11002,14 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>ORG: Etiqueta del piobacteriofago y una referencia. 212 ninos con amigdalitis aguda.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10978,10 +11070,14 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>ORG: Etiqueta del piobacteriofago y una referencia. 212 ninos con amigdalitis aguda.</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11106,10 +11202,14 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>ORG: Solo en la lista de referencias.</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11170,10 +11270,14 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>ORG: Solo en la lista de referencias, sus tres menciones.</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -12806,10 +12910,14 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>ORG: Espectro del coctel SniPha 360.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -13694,10 +13802,14 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>ORG: Cero menciones en 22.705 caracteres, en ninguna grafia. Rinosinusitis aguda.</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -13946,10 +14058,14 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>OFF: Articulo de cirugia reconstructiva de mediastinitis esternal. UNA mencion de fago en 43.000 caracteres, en una celda de tabla entre ocho antimicrobianos.</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -14442,10 +14558,14 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N216" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>INT: Endolisina de fago (79 menciones de lysin), no un bacteriofago.</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -14878,10 +14998,14 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>ORG: PDF correcto ya instalado (Europace 2020;22(4):597, DOI 10.1093/europace/euz319). Es un EP CASE EXPRESS de UNA pagina: varon de 41 anos, Marfan, infeccion de bolsillo de DAI e injerto vascular. CERO menciones de Pseudomonas o aeruginosa, y no nombra NINGUN microorganismo. La version completa del caso no esta en la revista, sino en una pagina de e-learning de la ESC. Fila extraida por un solo revisor.</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -15186,10 +15310,14 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N228" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>ORG: Espectro de SniPha 360; los cultivos dieron otra cosa.</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$N$235</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$N$234</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -533,7 +533,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>234 filas de datos</t>
+          <t>233 filas de datos</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N235"/>
+  <dimension ref="A1:N234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -859,7 +859,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>C. version en ingles disponible</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>eng 0.311 frente a spa 0.004; palabras: the of and in to a for with</t>
+          <t>original en rus, pero titulo principal en ingles sin corchetes y resumen integro en ingles de 5798 caracteres</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8514,10 +8514,14 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>IDI: Cuerpo del articulo en ruso: 94,1 % de caracteres cirilicos medidos sobre la pagina del editor (mediasphera.ru) SIN traduccion automatica. Lo latino es el resumen en ingles, las palabras clave y las referencias. NO existe version inglesa: /en/ devuelve 404, ?lang=en devuelve la misma pagina cirilica y /downloads/en/ no entrega PDF. El registro ya lo tenia como idioma_declarado=rus y aun asi ADMITIDO, porque el detector midio el resumen y no el cuerpo.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8547,7 +8551,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -8615,7 +8619,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -8679,7 +8683,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -8743,7 +8747,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -8807,7 +8811,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -8931,7 +8935,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -8995,7 +8999,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9059,7 +9063,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9127,7 +9131,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9195,7 +9199,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9259,12 +9263,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>C. version en ingles disponible</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>eng 0.300 frente a spa 0.005; palabras: the of and in to a for with</t>
+          <t>original en rus, pero titulo principal en ingles sin corchetes y resumen integro en ingles de 5292 caracteres</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -9294,10 +9298,14 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>IDI: Cuerpo del articulo en ruso: 77,9 % de caracteres cirilicos medidos sobre la pagina del editor (mediasphera.ru) SIN traduccion automatica. Lo latino es el resumen en ingles, las palabras clave y las referencias. NO existe version inglesa: /en/ devuelve 404, ?lang=en devuelve la misma pagina cirilica y /downloads/en/ no entrega PDF. El registro ya lo tenia como idioma_declarado=rus y aun asi ADMITIDO, porque el detector midio el resumen y no el cuerpo.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9327,7 +9335,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -9387,7 +9395,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -9451,7 +9459,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -9575,7 +9583,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -9699,7 +9707,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -9763,7 +9771,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -9887,7 +9895,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -9947,7 +9955,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10011,7 +10019,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10071,7 +10079,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10131,7 +10139,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -10195,7 +10203,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -10259,7 +10267,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -10323,7 +10331,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -10387,7 +10395,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -10451,7 +10459,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -10511,7 +10519,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -10575,7 +10583,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -10639,7 +10647,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -10703,7 +10711,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -10767,7 +10775,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -10810,22 +10818,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>R56334c0408</t>
+          <t>Ra969af6438</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>rus</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>exportacion de Scopus (brazo B) (campo de idioma)</t>
+          <t>Europe PMC (campo language)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10835,12 +10843,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>eng 0.268 frente a spa 0.000; palabras: the of and in to a with was</t>
+          <t>eng 0.251 frente a spa 0.000; palabras: the of and in to a with was</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10850,44 +10858,36 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2073</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>ВЛИЯНИЕ ИНГАЛЯЦИОННОЙ БАКТЕРИОФАГТЕРАПИИ НА МУКОЗАЛЬНЫЙ ИММУ</t>
-        </is>
-      </c>
+          <t>1384</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Russian Journal of Infection and Immunity</t>
+          <t>Viruses</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>INFLUENCE OF INHALED BACTERIOPHAGE THERAPY ON ORAL MUCOSAL IMMUNITY IN CHILDREN WITH ACUTE TONSILLITIS</t>
+          <t>Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-Resistant Pseudomonas aeruginosa Lef</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>excluido después</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>Informe no redactado en ingles ni en espanol (criterio de idioma, enmienda 2026-08-11); comprobado sobre el TEXTO COMPLETO en la web del editor: la revista rotula el cuerpo como Full Text (RUSSIAN) y solo el resumen esta en ingles. Los metadatos declaraban ingles.</t>
-        </is>
-      </c>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Ra969af6438</t>
+          <t>Ra4e9fbb2ff</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>126</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Europe PMC (campo language)</t>
+          <t>exportacion de Scopus (brazo A), emparejado por titulo</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>eng 0.251 frente a spa 0.000; palabras: the of and in to a with was</t>
+          <t>eng 0.295 frente a spa 0.000; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10922,31 +10922,35 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Viruses</t>
+          <t>International journal of pediatrics and adolescent medicine</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-Resistant Pseudomonas aeruginosa Lef</t>
+          <t>Application of bacteriophage therapy in the treatment of children with acute tonsillitis</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>ORG: Etiqueta del piobacteriofago y una referencia. 212 ninos con amigdalitis aguda.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Ra4e9fbb2ff</t>
+          <t>Rf175166f20</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10961,7 +10965,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>exportacion de Scopus (brazo A), emparejado por titulo</t>
+          <t>exportacion de Scopus (brazo A) (campo de idioma)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10971,7 +10975,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -10986,13 +10990,13 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>International journal of pediatrics and adolescent medicine</t>
+          <t xml:space="preserve">International Journal of Pediatrics and Adolescent Medicine </t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11014,12 +11018,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Rf175166f20</t>
+          <t>Re6bdbee7be</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>129</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -11029,7 +11033,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>exportacion de Scopus (brazo A) (campo de idioma)</t>
+          <t>Europe PMC (campo language)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -11039,12 +11043,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>eng 0.295 frente a spa 0.000; palabras: the of and in to a for with</t>
+          <t>eng 0.223 frente a spa 0.000; palabras: the of and in to for with was</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -11054,40 +11058,36 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">International Journal of Pediatrics and Adolescent Medicine </t>
+          <t>Antibiotics</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Application of bacteriophage therapy in the treatment of children with acute tonsillitis</t>
+          <t>Phage Therapy for Orthopaedic Infections: The First Three Cases from the United Kingdom</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>excluido después</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>ORG: Etiqueta del piobacteriofago y una referencia. 212 ninos con amigdalitis aguda.</t>
-        </is>
-      </c>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Re6bdbee7be</t>
+          <t>Rcfc3dae56a</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>130</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -11107,12 +11107,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>eng 0.223 frente a spa 0.000; palabras: the of and in to for with was</t>
+          <t>eng 0.217 frente a spa 0.000; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -11122,36 +11122,40 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Antibiotics</t>
+          <t>Nature communications</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>Phage Therapy for Orthopaedic Infections: The First Three Cases from the United Kingdom</t>
+          <t>Prolonged disease remission of the chronic immunological skin disorder hidradenitis suppurativa with adjunctiv</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>ORG: Solo en la lista de referencias.</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Rcfc3dae56a</t>
+          <t>R8b119ef966</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -11171,12 +11175,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>eng 0.217 frente a spa 0.000; palabras: the of and in to a for with</t>
+          <t>eng 0.263 frente a spa 0.011; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -11186,18 +11190,18 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Nature communications</t>
+          <t>International journal of antimicrobial agents</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>Prolonged disease remission of the chronic immunological skin disorder hidradenitis suppurativa with adjunctiv</t>
+          <t>Results of TOR001: An open-label single patient study using targeted bacteriophage therapy for the treatment o</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -11207,19 +11211,19 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>ORG: Solo en la lista de referencias.</t>
+          <t>ORG: Solo en la lista de referencias, sus tres menciones.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>R8b119ef966</t>
+          <t>Rc63b7d8aac</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>132</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -11239,12 +11243,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>eng 0.263 frente a spa 0.011; palabras: the of and in to a for with</t>
+          <t>eng 0.237 frente a spa 0.003; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -11254,35 +11258,31 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>International journal of antimicrobial agents</t>
+          <t>Indian Journal of Critical Care Medicine</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Results of TOR001: An open-label single patient study using targeted bacteriophage therapy for the treatment o</t>
+          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Management of Pressure Ulcers and Its Co</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>excluido después</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>ORG: Solo en la lista de referencias, sus tres menciones.</t>
-        </is>
-      </c>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R9504ca6b8e</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>eng 0.237 frente a spa 0.003; palabras: the of and in to a for with</t>
+          <t>eng 0.226 frente a spa 0.003; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -11322,13 +11322,13 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Indian Journal of Critical Care Medicine</t>
+          <t>Indian journal of critical care medicine</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -11346,12 +11346,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>R9504ca6b8e</t>
+          <t>Raa2e529a17</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>133</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Europe PMC (campo language)</t>
+          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -11371,12 +11371,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>eng 0.226 frente a spa 0.003; palabras: the of and in to a for with</t>
+          <t>eng 0.244 frente a spa 0.002; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11386,18 +11386,18 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Indian journal of critical care medicine</t>
+          <t>European urology, supplements</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Management of Pressure Ulcers and Its Co</t>
+          <t>Phage therapy for the treatment for urinary tract infection: results of in-vitro screenings and in-vivo applic</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -11410,12 +11410,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Raa2e529a17</t>
+          <t>Reba6a0e48c</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>134</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
+          <t>Europe PMC (campo language)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>eng 0.244 frente a spa 0.002; palabras: the of and in to a for with</t>
+          <t>eng 0.246 frente a por 0.011; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11450,18 +11450,18 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>European urology, supplements</t>
+          <t>Frontiers in microbiology</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Phage therapy for the treatment for urinary tract infection: results of in-vitro screenings and in-vivo applic</t>
+          <t>Adapted Bacteriophages for Treating Urinary Tract Infections.</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -11474,7 +11474,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Reba6a0e48c</t>
+          <t>R35097ad062</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Europe PMC (campo language)</t>
+          <t>exportacion de Scopus (brazo A), emparejado por titulo</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -11514,18 +11514,18 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Frontiers in microbiology</t>
+          <t>European urology, supplements</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Adapted Bacteriophages for Treating Urinary Tract Infections.</t>
+          <t>Adapted bacteriophages for treating urinary tract infections</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -11538,12 +11538,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>R35097ad062</t>
+          <t>Rf76e86bc31</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>135</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>exportacion de Scopus (brazo A), emparejado por titulo</t>
+          <t>Europe PMC (campo language)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -11563,12 +11563,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>eng 0.246 frente a por 0.011; palabras: the of and in to a for with</t>
+          <t>eng 0.267 frente a por 0.015; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11578,18 +11578,18 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>European urology, supplements</t>
+          <t>Frontiers in Medicine</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>Adapted bacteriophages for treating urinary tract infections</t>
+          <t>The Potential Innovative Use of Bacteriophages Within the DAC® Hydrogel to Treat Patients With Knee Megaprosth</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -11602,12 +11602,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Rf76e86bc31</t>
+          <t>Rfef2fe2708</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Europe PMC (campo language)</t>
+          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -11627,12 +11627,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>eng 0.267 frente a por 0.015; palabras: the of and in to a for with</t>
+          <t>eng 0.246 frente a ita 0.004; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11642,18 +11642,18 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Frontiers in Medicine</t>
+          <t>https://clinicaltrials.gov/study/NCT07698002</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>The Potential Innovative Use of Bacteriophages Within the DAC® Hydrogel to Treat Patients With Knee Megaprosth</t>
+          <t>"Debridement PhagE AnTibiotics for PJI"</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -11666,7 +11666,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Rfef2fe2708</t>
+          <t>R80ac05ea69</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11681,22 +11681,22 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>(indeterminado)</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>D. politica de idioma del registro</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>eng 0.246 frente a ita 0.004; palabras: the of and in to a for with</t>
+          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11706,15 +11706,11 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>https://clinicaltrials.gov/study/NCT07698002</t>
-        </is>
-      </c>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
           <t>"Debridement PhagE AnTibiotics for PJI"</t>
@@ -11730,12 +11726,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>R80ac05ea69</t>
+          <t>R0afae6295c</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>138</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -11750,17 +11746,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(indeterminado)</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>D. politica de idioma del registro</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
+          <t>eng 0.269 frente a por 0.038; palabras: the of for with by treatment</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11777,7 +11773,7 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
-          <t>"Debridement PhagE AnTibiotics for PJI"</t>
+          <t>PHRC-N/2015/AS-01 - Comparison of the efficacy of standard treatment associated with phage therapy versus stan</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -11790,12 +11786,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>R0afae6295c</t>
+          <t>R36411565f8</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>140</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11805,7 +11801,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>Europe PMC (campo language)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -11815,12 +11811,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>eng 0.269 frente a por 0.038; palabras: the of for with by treatment</t>
+          <t>eng 0.143 frente a spa 0.071; palabras: of for treatment</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11830,14 +11826,18 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>The Journal of heart and lung transplantation : the official publication of the International Society for Heart Transplantation</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>PHRC-N/2015/AS-01 - Comparison of the efficacy of standard treatment associated with phage therapy versus stan</t>
+          <t>Novel bacteriophage therapy for treatment of left ventricular assist device infection.</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -11850,12 +11850,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>R36411565f8</t>
+          <t>R09d4ba6319</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11865,22 +11865,22 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Europe PMC (campo language)</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>(indeterminado)</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>D. politica de idioma del registro</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>eng 0.143 frente a spa 0.071; palabras: of for treatment</t>
+          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11890,18 +11890,14 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>The Journal of heart and lung transplantation : the official publication of the International Society for Heart Transplantation</t>
-        </is>
-      </c>
+      <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Novel bacteriophage therapy for treatment of left ventricular assist device infection.</t>
+          <t>Bacteriophage Therapy in Tonsillitis</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -11914,12 +11910,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>R09d4ba6319</t>
+          <t>R45e6601a0b</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>143</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11929,22 +11925,22 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>(indeterminado)</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>D. politica de idioma del registro</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
+          <t>eng 0.158 frente a por 0.006; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11954,14 +11950,18 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=CTRI/2021/12/038527</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy in Tonsillitis</t>
+          <t>Chronic non healing ulcer and bacteriophage therapy</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -11974,12 +11974,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>R45e6601a0b</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>146</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
+          <t>Europe PMC (campo language)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11999,12 +11999,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>eng 0.158 frente a por 0.006; palabras: the of and in to a for with</t>
+          <t>eng 0.223 frente a por 0.010; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -12014,18 +12014,18 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=CTRI/2021/12/038527</t>
+          <t>Clinical infectious diseases : an official publication of the Infectious Diseases Society of America</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Chronic non healing ulcer and bacteriophage therapy</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized Phage Therapy: Production, Char</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -12038,17 +12038,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R4d6d6ce617</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>rus</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>C. version en ingles disponible</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>eng 0.223 frente a por 0.010; palabras: the of and in to a for with</t>
+          <t>original en rus, pero titulo principal en ingles sin corchetes y resumen integro en ingles de 793 caracteres</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -12078,61 +12078,69 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr"/>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Комплексное хирургическое лечение рецидивирующего постинъекц</t>
+        </is>
+      </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Clinical infectious diseases : an official publication of the Infectious Diseases Society of America</t>
+          <t>Pirogov Russian Journal of Surgery</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Customized Phage Therapy: Production, Char</t>
+          <t>Complex surgical treatment of recurrent post-injection abscess in a patient with systemic autoimmune disease</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N177" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>IDI: Cuerpo del articulo en ruso: 91,0 % de caracteres cirilicos medidos sobre la pagina del editor (mediasphera.ru) SIN traduccion automatica. Lo latino es el resumen en ingles, las palabras clave y las referencias. NO existe version inglesa: /en/ devuelve 404, ?lang=en devuelve la misma pagina cirilica y /downloads/en/ no entrega PDF. El registro ya lo tenia como idioma_declarado=rus y aun asi ADMITIDO, porque el detector midio el resumen y no el cuerpo.</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>R4d6d6ce617</t>
+          <t>R221c13dfc7</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>148</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>rus</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Europe PMC (campo language)</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>(indeterminado)</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>D. politica de idioma del registro</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>eng 0.261 frente a spa 0.000; palabras: the of and in to a for with</t>
+          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -12142,22 +12150,14 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>793</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>Комплексное хирургическое лечение рецидивирующего постинъекц</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>Pirogov Russian Journal of Surgery</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
-          <t>Complex surgical treatment of recurrent post-injection abscess in a patient with systemic autoimmune disease</t>
+          <t>Phage Therapy for the Treatment of Urinary Tract Infection</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -12170,12 +12170,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>R221c13dfc7</t>
+          <t>R717df5fd85</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>149</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -12185,22 +12185,22 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>(indeterminado)</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>D. politica de idioma del registro</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
+          <t>eng 0.206 frente a dan 0.008; palabras: the of and in to for with were</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -12210,14 +12210,18 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=ChiCTR2400094545</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>Phage Therapy for the Treatment of Urinary Tract Infection</t>
+          <t>Study to phages for prevention and treatment of difficult-to-treat resistant Pseudomonas aeruginosa infection</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -12230,12 +12234,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>R717df5fd85</t>
+          <t>Rea9d786d26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -12245,22 +12249,22 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>(indeterminado)</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>D. politica de idioma del registro</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>eng 0.206 frente a dan 0.008; palabras: the of and in to for with were</t>
+          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -12270,18 +12274,14 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=ChiCTR2400094545</t>
-        </is>
-      </c>
+      <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>Study to phages for prevention and treatment of difficult-to-treat resistant Pseudomonas aeruginosa infection</t>
+          <t>Use of Phage Therapy for Treatment of a Periprosthetic Joint Infection</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -12294,12 +12294,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Rea9d786d26</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>152</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -12309,22 +12309,22 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>Europe PMC (campo language)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>(indeterminado)</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>D. politica de idioma del registro</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
+          <t>eng 0.259 frente a por 0.004; palabras: the of and in to a with was</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -12334,14 +12334,18 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Antibiotics</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>Use of Phage Therapy for Treatment of a Periprosthetic Joint Infection</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -12354,12 +12358,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>R157654d30f</t>
+          <t>Rbb08a249dc</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>153</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -12369,7 +12373,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Europe PMC (campo language)</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -12379,12 +12383,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>eng 0.259 frente a por 0.004; palabras: the of and in to a with was</t>
+          <t>eng 0.211 frente a spa 0.000; palabras: of and for study</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12394,18 +12398,14 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>Antibiotics</t>
-        </is>
-      </c>
+      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated with Phages</t>
+          <t>Evaluation of Safety and Efficacy of Phage Therapy for Drug-resistant Bacterial Infections: An Exploratory, Pr</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -12418,12 +12418,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Rbb08a249dc</t>
+          <t>Re9525331c5</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>154</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -12433,7 +12433,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -12443,12 +12443,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>eng 0.211 frente a spa 0.000; palabras: of and for study</t>
+          <t>eng 0.249 frente a por 0.004; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12458,14 +12458,18 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>https://clinicaltrials.gov/ct2/show/NCT06370598</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Evaluation of Safety and Efficacy of Phage Therapy for Drug-resistant Bacterial Infections: An Exploratory, Pr</t>
+          <t>Phase 1/2a to Assess the Safety and Tolerability of TP-122A for the Treatment of Ventilator-Associated Pneumon</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -12478,7 +12482,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Re9525331c5</t>
+          <t>R6ce58a44af</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12493,7 +12497,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -12503,12 +12507,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>eng 0.249 frente a por 0.004; palabras: the of and in to a for with</t>
+          <t>eng 0.389 frente a spa 0.000; palabras: the of and to a for treatment</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12518,15 +12522,11 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>https://clinicaltrials.gov/ct2/show/NCT06370598</t>
-        </is>
-      </c>
+      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
           <t>Phase 1/2a to Assess the Safety and Tolerability of TP-122A for the Treatment of Ventilator-Associated Pneumon</t>
@@ -12542,12 +12542,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>R6ce58a44af</t>
+          <t>Rab18b3d474</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>155</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -12567,12 +12567,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>eng 0.389 frente a spa 0.000; palabras: the of and to a for treatment</t>
+          <t>eng 0.194 frente a por 0.010; palabras: the of and in to a with is</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12582,14 +12582,18 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=ChiCTR2500099778</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>Phase 1/2a to Assess the Safety and Tolerability of TP-122A for the Treatment of Ventilator-Associated Pneumon</t>
+          <t>Efficacy and safety of bacteriophage in treating severe drug-resistant lower respiratory tract infections in c</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -12602,12 +12606,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Rab18b3d474</t>
+          <t>Rbc25e976cb</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>156</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -12627,12 +12631,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>eng 0.194 frente a por 0.010; palabras: the of and in to a with is</t>
+          <t>eng 0.134 frente a por 0.009; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12642,18 +12646,18 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=ChiCTR2500099778</t>
+          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=CTIS2024-519856-94-00</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Efficacy and safety of bacteriophage in treating severe drug-resistant lower respiratory tract infections in c</t>
+          <t>Phase 2b Randomized, Double-Blind Study with Phage for CF Subjects with Pseudomonas Lung Infection</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -12666,12 +12670,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Rbc25e976cb</t>
+          <t>R18831247ea</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>157</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -12681,7 +12685,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
+          <t>Europe PMC (campo language)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -12691,12 +12695,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>eng 0.134 frente a por 0.009; palabras: the of and in to a for with</t>
+          <t>eng 0.278 frente a spa 0.000; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12706,18 +12710,18 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=CTIS2024-519856-94-00</t>
+          <t>The international journal of lower extremity wounds</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>Phase 2b Randomized, Double-Blind Study with Phage for CF Subjects with Pseudomonas Lung Infection</t>
+          <t>A Randomized, Placebo-controlled, Double-blind Clinical Trial of Bacteriophage Cocktails in Chronic Wound Infe</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -12730,12 +12734,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>R18831247ea</t>
+          <t>R1517c6529b</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -12745,22 +12749,22 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Europe PMC (campo language)</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>(indeterminado)</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>D. politica de idioma del registro</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>eng 0.278 frente a spa 0.000; palabras: the of and in to a for with</t>
+          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12770,18 +12774,14 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>The international journal of lower extremity wounds</t>
-        </is>
-      </c>
+      <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
-          <t>A Randomized, Placebo-controlled, Double-blind Clinical Trial of Bacteriophage Cocktails in Chronic Wound Infe</t>
+          <t>Bacteriophage Effects on Pseudomonas Aeruginosa</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -12794,12 +12794,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>R1517c6529b</t>
+          <t>R4ad09fd8ae</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>159</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -12809,22 +12809,22 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>Europe PMC (campo language)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>(indeterminado)</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>D. politica de idioma del registro</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
+          <t>eng 0.155 frente a ita 0.003; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12834,32 +12834,40 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Antibiotics</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>Bacteriophage Effects on Pseudomonas Aeruginosa</t>
+          <t>Bacteriophage-Enriched Galenic for Intrapericardial Ventricular Assist Device Infection</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N189" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>ORG: Espectro del coctel SniPha 360.</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>R4ad09fd8ae</t>
+          <t>R91b5b8d9ef</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>160</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12869,7 +12877,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Europe PMC (campo language)</t>
+          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12879,12 +12887,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>eng 0.155 frente a ita 0.003; palabras: the of and in to a for with</t>
+          <t>eng 0.145 frente a spa 0.000; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12894,40 +12902,36 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Antibiotics</t>
+          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=ChiCTR2600125813</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>Bacteriophage-Enriched Galenic for Intrapericardial Ventricular Assist Device Infection</t>
+          <t>A Randomized Controlled Trial on the Safety and Efficacy of Phage Cocktail Therapy for Multidrug-Resistant Bac</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>excluido después</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr">
-        <is>
-          <t>ORG: Espectro del coctel SniPha 360.</t>
-        </is>
-      </c>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>R91b5b8d9ef</t>
+          <t>R71d2c2521c</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>161</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12937,22 +12941,22 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>(indeterminado)</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>D. politica de idioma del registro</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>eng 0.145 frente a spa 0.000; palabras: the of and in to a for with</t>
+          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12962,18 +12966,14 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=ChiCTR2600125813</t>
-        </is>
-      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>A Randomized Controlled Trial on the Safety and Efficacy of Phage Cocktail Therapy for Multidrug-Resistant Bac</t>
+          <t>MP101 in Adults With Acute Pseudomonas Aeruginosa Pneumonia</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -12986,12 +12986,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>R71d2c2521c</t>
+          <t>R509b5448ca</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>162</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -13001,22 +13001,22 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>(indeterminado)</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>D. politica de idioma del registro</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
+          <t>eng 0.201 frente a por 0.011; palabras: the of and in to a with is</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -13026,14 +13026,18 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=KCT0011717</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>MP101 in Adults With Acute Pseudomonas Aeruginosa Pneumonia</t>
+          <t>Phase 1 Study of MP101 in Adults With Acute Pseudomonas aeruginosa Pneumonia</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -13046,12 +13050,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>R509b5448ca</t>
+          <t>R3ec3a782bb</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>164</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -13061,7 +13065,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
+          <t>Europe PMC (campo language)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -13071,12 +13075,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>eng 0.201 frente a por 0.011; palabras: the of and in to a with is</t>
+          <t>eng 0.264 frente a spa 0.009; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -13086,18 +13090,18 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=KCT0011717</t>
+          <t>Viruses</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Phase 1 Study of MP101 in Adults With Acute Pseudomonas aeruginosa Pneumonia</t>
+          <t>Bacteriophage Application for Difficult-to-treat Musculoskeletal Infections: Development of a Standardized Mul</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -13110,12 +13114,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>R3ec3a782bb</t>
+          <t>R9b7fc7c6a6</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>165</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -13135,12 +13139,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>eng 0.264 frente a spa 0.009; palabras: the of and in to a for with</t>
+          <t>eng 0.299 frente a por 0.004; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -13150,18 +13154,18 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Viruses</t>
+          <t>The international journal of lower extremity wounds</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>Bacteriophage Application for Difficult-to-treat Musculoskeletal Infections: Development of a Standardized Mul</t>
+          <t>Use of Customized Bacteriophages in the Treatment of Chronic Nonhealing Wounds: A Prospective Study.</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -13174,12 +13178,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>R9b7fc7c6a6</t>
+          <t>Re6084b7743</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>167</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -13199,12 +13203,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>eng 0.299 frente a por 0.004; palabras: the of and in to a for with</t>
+          <t>eng 0.207 frente a por 0.012; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -13214,7 +13218,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -13225,7 +13229,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>Use of Customized Bacteriophages in the Treatment of Chronic Nonhealing Wounds: A Prospective Study.</t>
+          <t>Biological Therapy on Infected Traumatic Wounds: A Case-Control Study.</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -13238,12 +13242,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Re6084b7743</t>
+          <t>Rd7ea09ed5c</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>169</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -13263,12 +13267,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>eng 0.207 frente a por 0.012; palabras: the of and in to a for with</t>
+          <t>eng 0.226 frente a spa 0.004; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -13278,18 +13282,18 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>The international journal of lower extremity wounds</t>
+          <t>Virus research</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>Biological Therapy on Infected Traumatic Wounds: A Case-Control Study.</t>
+          <t>Safety and tolerability of bronchoscopic and nebulised administration of bacteriophage.</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -13302,12 +13306,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Rd7ea09ed5c</t>
+          <t>Rc513775cd3</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>170</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -13317,7 +13321,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Europe PMC (campo language)</t>
+          <t>exportacion de Scopus (brazo B) (campo de idioma)</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -13327,12 +13331,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>eng 0.226 frente a spa 0.004; palabras: the of and in to a for with</t>
+          <t>eng 0.172 frente a spa 0.008; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13342,18 +13346,18 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>816</t>
         </is>
       </c>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Virus research</t>
+          <t>Annals of Vascular Surgery - Brief Reports and Innovations</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>Safety and tolerability of bronchoscopic and nebulised administration of bacteriophage.</t>
+          <t>Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aortic aneurysm</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -13366,12 +13370,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Rc513775cd3</t>
+          <t>Rb65634196d</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>171</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -13381,7 +13385,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>exportacion de Scopus (brazo B) (campo de idioma)</t>
+          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -13391,12 +13395,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>eng 0.172 frente a spa 0.008; palabras: the of and in to a for with</t>
+          <t>eng 0.241 frente a por 0.017; palabras: the of and in to a with its</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13406,18 +13410,18 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>348</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Annals of Vascular Surgery - Brief Reports and Innovations</t>
+          <t>https://clinicaltrials.gov/study/NCT07612605</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aortic aneurysm</t>
+          <t>Yiqi Huoxue Jiedu Formula Combined With Bacteriophages in the Treatment of Severe Pneumonia</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -13430,7 +13434,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Rb65634196d</t>
+          <t>R7312fa024a</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13445,7 +13449,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -13455,12 +13459,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>eng 0.241 frente a por 0.017; palabras: the of and in to a with its</t>
+          <t>eng 0.308 frente a spa 0.000; palabras: the of in with treatment</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13470,15 +13474,11 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>https://clinicaltrials.gov/study/NCT07612605</t>
-        </is>
-      </c>
+      <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
           <t>Yiqi Huoxue Jiedu Formula Combined With Bacteriophages in the Treatment of Severe Pneumonia</t>
@@ -13494,12 +13494,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>R7312fa024a</t>
+          <t>R21af282137</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>172</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -13519,12 +13519,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>eng 0.308 frente a spa 0.000; palabras: the of in with treatment</t>
+          <t>eng 0.170 frente a ita 0.008; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13534,14 +13534,18 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=CTRI/2023/11/059899</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>Yiqi Huoxue Jiedu Formula Combined With Bacteriophages in the Treatment of Severe Pneumonia</t>
+          <t>Study to assess the Safety and Efficacy of Bacteriophage in the treatment of Diabetic foot infection</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -13554,12 +13558,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>R21af282137</t>
+          <t>R4a198d51c5</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>173</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -13569,7 +13573,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
+          <t>exportacion de Scopus (brazo B), emparejado por titulo</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -13579,12 +13583,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>eng 0.170 frente a ita 0.008; palabras: the of and in to a for with</t>
+          <t>eng 0.369 frente a por 0.006; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -13594,18 +13598,18 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=CTRI/2023/11/059899</t>
+          <t>Surgical Chronicles</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>Study to assess the Safety and Efficacy of Bacteriophage in the treatment of Diabetic foot infection</t>
+          <t>Use of bacteriophages in the treatment of infected wounds in patients who have allergy to antibiotics</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -13618,12 +13622,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>R4a198d51c5</t>
+          <t>R7238cb8c19</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>177</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -13633,7 +13637,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>exportacion de Scopus (brazo B), emparejado por titulo</t>
+          <t>Europe PMC (campo language)</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -13643,12 +13647,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>eng 0.369 frente a por 0.006; palabras: the of and in to a for with</t>
+          <t>eng 0.244 frente a ita 0.018; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13658,18 +13662,18 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Surgical Chronicles</t>
+          <t>Otolaryngologia polska = The Polish otolaryngology</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>Use of bacteriophages in the treatment of infected wounds in patients who have allergy to antibiotics</t>
+          <t>A randomized, double-blind, placebo- -controlled study to investigate the use of bacteriophages in patients wi</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -13682,12 +13686,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>R7238cb8c19</t>
+          <t>R58e4f5ffa4</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>178</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -13707,12 +13711,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>eng 0.244 frente a ita 0.018; palabras: the of and in to a for with</t>
+          <t>eng 0.319 frente a spa 0.000; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13722,36 +13726,40 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Otolaryngologia polska = The Polish otolaryngology</t>
+          <t>Wiadomosci lekarskie (Warsaw, Poland : 1960)</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>A randomized, double-blind, placebo- -controlled study to investigate the use of bacteriophages in patients wi</t>
+          <t xml:space="preserve">CLINICAL AND LABORATORY JUSTIFICATION FOR USE OF POLYVALENT BACTERIOPHAGE IN TECHNIQUE OF DELAYED PRESCRIBING </t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>ORG: Cero menciones en 22.705 caracteres, en ninguna grafia. Rinosinusitis aguda.</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>R58e4f5ffa4</t>
+          <t>Rf2699aa65a</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>181</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -13771,12 +13779,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>eng 0.319 frente a spa 0.000; palabras: the of and in to a for with</t>
+          <t>eng 0.267 frente a ita 0.005; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13786,40 +13794,36 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Wiadomosci lekarskie (Warsaw, Poland : 1960)</t>
+          <t>Viruses</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLINICAL AND LABORATORY JUSTIFICATION FOR USE OF POLYVALENT BACTERIOPHAGE IN TECHNIQUE OF DELAYED PRESCRIBING </t>
+          <t xml:space="preserve">Short-Term Outcomes of Phage-Antibiotic Combination Treatment in Adult Patients with Periprosthetic Hip Joint </t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>excluido después</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>ORG: Cero menciones en 22.705 caracteres, en ninguna grafia. Rinosinusitis aguda.</t>
-        </is>
-      </c>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Rf2699aa65a</t>
+          <t>R4360ac52ef</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>182</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -13829,7 +13833,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Europe PMC (campo language)</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -13839,12 +13843,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>eng 0.267 frente a ita 0.005; palabras: the of and in to a for with</t>
+          <t>eng 0.125 frente a spa 0.000; palabras: of in to a for with study patients</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13854,18 +13858,14 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>Viruses</t>
-        </is>
-      </c>
+      <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Short-Term Outcomes of Phage-Antibiotic Combination Treatment in Adult Patients with Periprosthetic Hip Joint </t>
+          <t>Phase 1b/2a Randomized Double-blind Study to Investigate Safety Tolerability PK PD Preliminary Efficacy of Ora</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -13878,12 +13878,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>R4360ac52ef</t>
+          <t>R419c6f6d67</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>184</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>Europe PMC (campo language)</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>B. campo de idioma de la fuente</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>eng 0.125 frente a spa 0.000; palabras: of in to a for with study patients</t>
+          <t>Europe PMC (campo language) declara eng; texto insuficiente para corroborar (eng 0.077 frente a spa 0.077: margen escaso)</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13918,14 +13918,18 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>JAAD Case Reports</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>Phase 1b/2a Randomized Double-blind Study to Investigate Safety Tolerability PK PD Preliminary Efficacy of Ora</t>
+          <t>Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -13938,12 +13942,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>R419c6f6d67</t>
+          <t>R667ca55ab2</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>185</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13963,12 +13967,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>B. campo de idioma de la fuente</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Europe PMC (campo language) declara eng; texto insuficiente para corroborar (eng 0.077 frente a spa 0.077: margen escaso)</t>
+          <t>eng 0.190 frente a spa 0.004; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13978,36 +13982,40 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>JAAD Case Reports</t>
+          <t>Journal of Plastic, Reconstructive and Aesthetic Surgery</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection</t>
+          <t>The management of sternal mediastinitis in heart and lung transplant patients: An 8-year experience and applic</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N207" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>OFF: Articulo de cirugia reconstructiva de mediastinitis esternal. UNA mencion de fago en 43.000 caracteres, en una celda de tabla entre ocho antimicrobianos.</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>R667ca55ab2</t>
+          <t>R82ba22a1d4</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>186</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -14017,7 +14025,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Europe PMC (campo language)</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -14027,12 +14035,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>eng 0.190 frente a spa 0.004; palabras: the of and in to a for with</t>
+          <t>eng 0.192 frente a por 0.038; palabras: the and to a study</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -14042,40 +14050,32 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>Journal of Plastic, Reconstructive and Aesthetic Surgery</t>
-        </is>
-      </c>
+      <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
-          <t>The management of sternal mediastinitis in heart and lung transplant patients: An 8-year experience and applic</t>
+          <t>Phage4Cure-001 - A three part randomized, double-blind, placebo-controlled, parallel group SAD and MD clinical</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>excluido después</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>OFF: Articulo de cirugia reconstructiva de mediastinitis esternal. UNA mencion de fago en 43.000 caracteres, en una celda de tabla entre ocho antimicrobianos.</t>
-        </is>
-      </c>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>R82ba22a1d4</t>
+          <t>Rc6b6f2d004</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>187</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -14095,12 +14095,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>eng 0.192 frente a por 0.038; palabras: the and to a study</t>
+          <t>eng 0.231 frente a spa 0.000; palabras: the of and to a study</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -14117,7 +14117,7 @@
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
-          <t>Phage4Cure-001 - A three part randomized, double-blind, placebo-controlled, parallel group SAD and MD clinical</t>
+          <t xml:space="preserve">Phage4Cure-001 - A two part, randomized, double-blind, placebo-controlled, parallel group SAD and MD clinical </t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -14130,12 +14130,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Rc6b6f2d004</t>
+          <t>R95ed8fa775</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -14155,12 +14155,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>eng 0.231 frente a spa 0.000; palabras: the of and to a study</t>
+          <t>eng 0.220 frente a por 0.015; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -14170,14 +14170,18 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Nephrology dialysis transplantation</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phage4Cure-001 - A two part, randomized, double-blind, placebo-controlled, parallel group SAD and MD clinical </t>
+          <t>Potential treatment method of recurrent urinary tract infection in postmenopausal kidney transplant recipients</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -14190,12 +14194,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>R95ed8fa775</t>
+          <t>R03a7447506</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>190</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -14215,12 +14219,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>eng 0.220 frente a por 0.015; palabras: the of and in to a for with</t>
+          <t>eng 0.212 frente a por 0.005; palabras: the of in to a for with is</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -14230,18 +14234,18 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Nephrology dialysis transplantation</t>
+          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=ChiCTR2600116642</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>Potential treatment method of recurrent urinary tract infection in postmenopausal kidney transplant recipients</t>
+          <t>Phage-Antibiotic Combination Therapy for Multidrug-Resistant Infections: a Prospective Study</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -14254,12 +14258,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>R03a7447506</t>
+          <t>Rb4a8aeb7e8</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>191</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -14269,7 +14273,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -14279,12 +14283,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>eng 0.212 frente a por 0.005; palabras: the of in to a for with is</t>
+          <t>eng 0.130 frente a spa 0.000; palabras: in to a study treatment</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -14294,18 +14298,14 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=ChiCTR2600116642</t>
-        </is>
-      </c>
+      <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
-          <t>Phage-Antibiotic Combination Therapy for Multidrug-Resistant Infections: a Prospective Study</t>
+          <t>BMX-04-002 - A Phase 2b, Randomized, Double-Blind, Placebo-Controlled, Multicenter Study to Evaluate Nebulized</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -14318,12 +14318,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Rb4a8aeb7e8</t>
+          <t>Rb7ef70c6bc</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>192</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -14343,12 +14343,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>eng 0.130 frente a spa 0.000; palabras: in to a study treatment</t>
+          <t>eng 0.429 frente a spa 0.000; palabras: the of and on</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -14365,7 +14365,7 @@
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
-          <t>BMX-04-002 - A Phase 2b, Randomized, Double-Blind, Placebo-Controlled, Multicenter Study to Evaluate Nebulized</t>
+          <t>The Effect of Supraglottic and Oropharyngeal Decontamination on the Incidence of Ventilator-associated Pneumon</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -14378,7 +14378,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Rb7ef70c6bc</t>
+          <t>Rf84921307f</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -14403,12 +14403,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>eng 0.429 frente a spa 0.000; palabras: the of and on</t>
+          <t>eng 0.256 frente a por 0.013; palabras: the of and in a for with is</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -14418,11 +14418,15 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>499</t>
         </is>
       </c>
       <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>https://clinicaltrials.gov/show/NCT04325685</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>The Effect of Supraglottic and Oropharyngeal Decontamination on the Incidence of Ventilator-associated Pneumon</t>
@@ -14438,12 +14442,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Rf84921307f</t>
+          <t>Rb9d3a3c831</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>199</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -14453,7 +14457,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
+          <t>Europe PMC (campo language)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -14463,12 +14467,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>eng 0.256 frente a por 0.013; palabras: the of and in a for with is</t>
+          <t>eng 0.255 frente a por 0.007; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14478,36 +14482,40 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>https://clinicaltrials.gov/show/NCT04325685</t>
+          <t>Frontiers in Medicine</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>The Effect of Supraglottic and Oropharyngeal Decontamination on the Incidence of Ventilator-associated Pneumon</t>
+          <t>Successful use of a phage endolysin for treatment of chronic pelvic pain syndrome/chronic bacterial prostatiti</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N215" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>INT: Endolisina de fago (79 menciones de lysin), no un bacteriofago.</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Rb9d3a3c831</t>
+          <t>R4c32396f34</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -14517,7 +14525,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Europe PMC (campo language)</t>
+          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -14527,12 +14535,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>eng 0.255 frente a por 0.007; palabras: the of and in to a for with</t>
+          <t>eng 0.228 frente a spa 0.000; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14542,35 +14550,31 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>755</t>
         </is>
       </c>
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Frontiers in Medicine</t>
+          <t>https://clinicaltrials.gov/ct2/show/NCT06998043</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>Successful use of a phage endolysin for treatment of chronic pelvic pain syndrome/chronic bacterial prostatiti</t>
+          <t>Study With Phage for CF Subjects With Pseudomonas Lung Infection</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>excluido después</t>
-        </is>
-      </c>
-      <c r="N216" t="inlineStr">
-        <is>
-          <t>INT: Endolisina de fago (79 menciones de lysin), no un bacteriofago.</t>
-        </is>
-      </c>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>R4c32396f34</t>
+          <t>R0460c7eae8</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14585,22 +14589,22 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>(indeterminado)</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>D. politica de idioma del registro</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>eng 0.228 frente a spa 0.000; palabras: the of and in to a for with</t>
+          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14610,15 +14614,11 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>https://clinicaltrials.gov/ct2/show/NCT06998043</t>
-        </is>
-      </c>
+      <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr">
         <is>
           <t>Study With Phage for CF Subjects With Pseudomonas Lung Infection</t>
@@ -14634,12 +14634,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>R0460c7eae8</t>
+          <t>R07e092ec2e</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -14649,22 +14649,22 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>(indeterminado)</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>D. politica de idioma del registro</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
+          <t>eng 0.241 frente a spa 0.000; palabras: the of and in to a for with</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14674,14 +14674,18 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=IRCT20250108064318N1</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>Study With Phage for CF Subjects With Pseudomonas Lung Infection</t>
+          <t>The effect of Bacteriophage on Diabetic foot Ulcers</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -14694,12 +14698,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>R07e092ec2e</t>
+          <t>Rc08e36041c</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>203</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -14709,7 +14713,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -14719,12 +14723,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>eng 0.241 frente a spa 0.000; palabras: the of and in to a for with</t>
+          <t>eng 0.350 frente a spa 0.000; palabras: the of and a for study treatment</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14734,18 +14738,14 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=IRCT20250108064318N1</t>
-        </is>
-      </c>
+      <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
-          <t>The effect of Bacteriophage on Diabetic foot Ulcers</t>
+          <t>A Prospective, Randomized, Double-Blind Controlled Study of WPP-201 for the Safety and Efficacy of Treatment o</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -14758,12 +14758,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Rc08e36041c</t>
+          <t>R9483d0060a</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>204</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -14778,17 +14778,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>(indeterminado)</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>D. politica de idioma del registro</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>eng 0.350 frente a spa 0.000; palabras: the of and a for study treatment</t>
+          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14805,7 +14805,7 @@
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
-          <t>A Prospective, Randomized, Double-Blind Controlled Study of WPP-201 for the Safety and Efficacy of Treatment o</t>
+          <t>Antibacterial Treatment Against Diarrhea in Oral Rehydration Solution</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -14818,37 +14818,37 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>R9483d0060a</t>
+          <t>R9e51826497</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>205</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>spa</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>exportacion de SciELO, emparejado por titulo</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>(indeterminado)</t>
+          <t>spa</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>D. politica de idioma del registro</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
+          <t>spa 0.135 frente a por 0.012; palabras: el la los las de del y en</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14858,14 +14858,18 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Revista Cubana de Angiología y Cirugía Vascular</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>Antibacterial Treatment Against Diarrhea in Oral Rehydration Solution</t>
+          <t>Beneficios obtenidos con el empleo de bacteriófagos en el tratamiento de infecciones crónicas</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -14878,37 +14882,37 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>R9e51826497</t>
+          <t>R65b56c8408</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>spa</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>exportacion de SciELO, emparejado por titulo</t>
+          <t>Europe PMC (campo language)</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>spa</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>spa 0.135 frente a por 0.012; palabras: el la los las de del y en</t>
+          <t>eng 0.150 frente a spa 0.050; palabras: of and a treatment</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14918,36 +14922,40 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Revista Cubana de Angiología y Cirugía Vascular</t>
+          <t>Europace : European pacing, arrhythmias, and cardiac electrophysiology : journal of the working groups on cardiac pacing, arrhythmias, and cardiac cellular electrophysiology of the European Society of Cardiology</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>Beneficios obtenidos con el empleo de bacteriófagos en el tratamiento de infecciones crónicas</t>
+          <t>Successful bacteriophage treatment of infection involving cardiac implantable electronic device and aortic gra</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N222" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>ORG: PDF correcto ya instalado (Europace 2020;22(4):597, DOI 10.1093/europace/euz319). Es un EP CASE EXPRESS de UNA pagina: varon de 41 anos, Marfan, infeccion de bolsillo de DAI e injerto vascular. CERO menciones de Pseudomonas o aeruginosa, y no nombra NINGUN microorganismo. La version completa del caso no esta en la revista, sino en una pagina de e-learning de la ESC. Fila extraida por un solo revisor.</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>R65b56c8408</t>
+          <t>R48f287c11f</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>208</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14967,12 +14975,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>eng 0.150 frente a spa 0.050; palabras: of and a treatment</t>
+          <t>eng 0.247 frente a por 0.013; palabras: the of and to a with by on</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14982,40 +14990,36 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>461</t>
         </is>
       </c>
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Europace : European pacing, arrhythmias, and cardiac electrophysiology : journal of the working groups on cardiac pacing, arrhythmias, and cardiac cellular electrophysiology of the European Society of Cardiology</t>
+          <t>European journal of cardio-thoracic surgery : official journal of the European Association for Cardio-thoracic Surgery</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>Successful bacteriophage treatment of infection involving cardiac implantable electronic device and aortic gra</t>
+          <t>Treatment of chronic left ventricular assist device infection with local application of bacteriophages.</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>excluido después</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>ORG: PDF correcto ya instalado (Europace 2020;22(4):597, DOI 10.1093/europace/euz319). Es un EP CASE EXPRESS de UNA pagina: varon de 41 anos, Marfan, infeccion de bolsillo de DAI e injerto vascular. CERO menciones de Pseudomonas o aeruginosa, y no nombra NINGUN microorganismo. La version completa del caso no esta en la revista, sino en una pagina de e-learning de la ESC. Fila extraida por un solo revisor.</t>
-        </is>
-      </c>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>R48f287c11f</t>
+          <t>R4dfe961e12</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -15025,22 +15029,22 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Europe PMC (campo language)</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>(indeterminado)</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>D. politica de idioma del registro</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>eng 0.247 frente a por 0.013; palabras: the of and to a with by on</t>
+          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -15050,18 +15054,14 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>European journal of cardio-thoracic surgery : official journal of the European Association for Cardio-thoracic Surgery</t>
-        </is>
-      </c>
+      <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
-          <t>Treatment of chronic left ventricular assist device infection with local application of bacteriophages.</t>
+          <t>Phage Safety Retrospective Cohort Study</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -15074,12 +15074,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>R4dfe961e12</t>
+          <t>Rcc006883b6</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -15094,17 +15094,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>(indeterminado)</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>D. politica de idioma del registro</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
+          <t>eng 0.294 frente a spa 0.000; palabras: the of and in a study</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -15121,7 +15121,7 @@
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
-          <t>Phage Safety Retrospective Cohort Study</t>
+          <t xml:space="preserve">A Study Investigating the Safety, Recovery, and Pharmacodynamics of Multiple Oral Administrations of SNIPR001 </t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -15134,12 +15134,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Rcc006883b6</t>
+          <t>R1db63ef613</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>211</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -15154,17 +15154,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>(indeterminado)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>D. politica de idioma del registro</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>eng 0.294 frente a spa 0.000; palabras: the of and in a study</t>
+          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -15181,7 +15181,7 @@
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Study Investigating the Safety, Recovery, and Pharmacodynamics of Multiple Oral Administrations of SNIPR001 </t>
+          <t>BActeriophages To Treat Liver Disease Eliminating Harmful Bacteria (BATTLE)</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -15194,12 +15194,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>R1db63ef613</t>
+          <t>R466bca70fe</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>212</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -15209,22 +15209,22 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>Europe PMC (campo language)</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>(indeterminado)</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>D. politica de idioma del registro</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
+          <t>eng 0.277 frente a spa 0.000; palabras: the of and in a with are by</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -15234,32 +15234,40 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>418</t>
         </is>
       </c>
       <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Antibiotics</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>BActeriophages To Treat Liver Disease Eliminating Harmful Bacteria (BATTLE)</t>
+          <t>Local Treatment of Driveline Infection with Bacteriophages</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N227" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>ORG: Espectro de SniPha 360; los cultivos dieron otra cosa.</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>R466bca70fe</t>
+          <t>Rf56ec00127</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>213</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -15269,22 +15277,22 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Europe PMC (campo language)</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>(indeterminado)</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>D. politica de idioma del registro</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>eng 0.277 frente a spa 0.000; palabras: the of and in a with are by</t>
+          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -15294,40 +15302,32 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>Antibiotics</t>
-        </is>
-      </c>
+      <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
-          <t>Local Treatment of Driveline Infection with Bacteriophages</t>
+          <t>Mayo Clinic Phage Program Biobank</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>excluido después</t>
-        </is>
-      </c>
-      <c r="N228" t="inlineStr">
-        <is>
-          <t>ORG: Espectro de SniPha 360; los cultivos dieron otra cosa.</t>
-        </is>
-      </c>
+          <t>incluido</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Rf56ec00127</t>
+          <t>Rd218ea735a</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>214</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -15369,7 +15369,7 @@
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
-          <t>Mayo Clinic Phage Program Biobank</t>
+          <t>Phage Safety Cohort Study</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -15382,12 +15382,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Rd218ea735a</t>
+          <t>R74adbef4c7</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>215</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -15429,7 +15429,7 @@
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
-          <t>Phage Safety Cohort Study</t>
+          <t>Clinical Trial to Demonstrate the Safety and Efficacy of DUOFAG®</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -15442,12 +15442,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>R74adbef4c7</t>
+          <t>R5e5bac7d74</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>216</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -15489,7 +15489,7 @@
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
-          <t>Clinical Trial to Demonstrate the Safety and Efficacy of DUOFAG®</t>
+          <t>Treatment Chronic UTI Post Kidney Transplant</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -15502,12 +15502,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>R5e5bac7d74</t>
+          <t>R5dd521bed2</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>217</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -15517,22 +15517,22 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>(indeterminado)</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>D. politica de idioma del registro</t>
+          <t>A. título y resumen probados</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
+          <t>eng 0.130 frente a spa 0.000; palabras: the of and in for at</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -15542,14 +15542,18 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>820</t>
         </is>
       </c>
       <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=CTRI/2024/03/064013</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>Treatment Chronic UTI Post Kidney Transplant</t>
+          <t>Evaluate the effect of bacteriophage in pressure ulcers</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -15562,12 +15566,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>R5dd521bed2</t>
+          <t>R58c987406c</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>218</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -15577,22 +15581,22 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Cochrane CENTRAL indexa titulo y resumen en ingles</t>
+          <t>ficha de registro de ensayo: el registro publica en ingles</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>(indeterminado)</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>A. texto probado</t>
+          <t>D. politica de idioma del registro</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>eng 0.130 frente a spa 0.000; palabras: the of and in for at</t>
+          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -15602,18 +15606,14 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>https://trialsearch.who.int/Trial2.aspx?TrialID=CTRI/2024/03/064013</t>
-        </is>
-      </c>
+      <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
-          <t>Evaluate the effect of bacteriophage in pressure ulcers</t>
+          <t>Biomarkers of Phage Treatment Response in NTM and Other Infections</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -15626,37 +15626,37 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>R58c987406c</t>
+          <t>R451bce0c4a</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>219</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>eng</t>
+          <t>rus</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>ficha de registro de ensayo: el registro publica en ingles</t>
+          <t>Europe PMC (campo language)</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>(indeterminado)</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>D. politica de idioma del registro</t>
+          <t>C. version en ingles disponible</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>42 CFR 11 y la politica de la NLM exigen que el registro se presente en ingles</t>
+          <t>original en rus, pero titulo principal en ingles sin corchetes y resumen integro en ingles de 1557 caracteres</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15666,93 +15666,37 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Использование лекарственных препаратов бактериофагов в компл</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Pirogov Russian Journal of Surgery</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>Biomarkers of Phage Treatment Response in NTM and Other Infections</t>
+          <t>Bacteriophages in complex treatment of septic diseases of the hand</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>R451bce0c4a</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>rus</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>Europe PMC (campo language)</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>eng</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>A. texto probado</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>eng 0.268 frente a spa 0.000; palabras: the of and in to for with was</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>admitido</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>Использование лекарственных препаратов бактериофагов в компл</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>Pirogov Russian Journal of Surgery</t>
-        </is>
-      </c>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t>Bacteriophages in complex treatment of septic diseases of the hand</t>
-        </is>
-      </c>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N235" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>IDI: Cuerpo del articulo en ruso: 93,0 % de caracteres cirilicos medidos sobre la pagina del editor (mediasphera.ru) SIN traduccion automatica. Lo latino es el resumen en ingles, las palabras clave y las referencias. NO existe version inglesa: /en/ devuelve 404, ?lang=en devuelve la misma pagina cirilica y /downloads/en/ no entrega PDF. El registro ya lo tenia como idioma_declarado=rus y aun asi ADMITIDO, porque el detector midio el resumen y no el cuerpo. ADEMAS falla por poblacion: 111 pacientes con infecciones purulentas de la mano, patogenos predominantes Staphylococcus y Streptococcus; P. aeruginosa solo aparece en la composicion del piobacteriofago.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N235"/>
+  <autoFilter ref="A1:N234"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -725,7 +725,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-01</t>
+          <t>Generado el 2026-09-02</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -13678,10 +13678,14 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>ORG: Texto completo leido en linea el 1 de septiembre de 2026, en la version INGLESA del propio editor (otolaryngologypl.com/article/150084/en), no una traduccion. Son 40 pacientes adultos con rinosinusitis cronica con polipos nasales, operados por cirugia endoscopica funcional; 20 recibieron gel intranasal con fagos y 20 placebo. P. aeruginosa aparece UNA sola vez en todo el articulo, en el espectro declarado del producto: el gel Otophag contiene 32 tipos de fagos y la lista de bacterias que inhibe la incluye. Lo que se midio en los pacientes fue Streptococci, Enterobacteriaceae y Staphylococci. Ningun paciente tiene P. aeruginosa documentada. Mismo patron que las otras diez exclusiones ORG. El idioma SI cumple: el editor publica version inglesa propia.</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -10362,10 +10362,14 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>NOREC: No se consiguio el texto completo. NO falla ningun criterio de §2.2: se excluye por no haberse podido leer. Comprobada su disponibilidad contra Europe PMC, OpenAlex y Semantic Scholar; la unica copia esta en el Zurich Open Repository, es la version ENVIADA --previa a revision por pares-- y el repositorio esta tras una barrera anti-bots. Decision de D. Valdiviezo del 2026-09-02, tomada conociendo que el criterio aplicado de forma consistente sacaria a los 26 no recuperados.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10426,10 +10430,14 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>NOREC: No se consiguio el texto completo. NO falla ningun criterio de §2.2: se excluye por no haberse podido leer. Comprobada su disponibilidad contra Europe PMC, OpenAlex y Semantic Scholar; la unica copia esta en el Zurich Open Repository, es la version ENVIADA --previa a revision por pares-- y el repositorio esta tras una barrera anti-bots. Decision de D. Valdiviezo del 2026-09-02, tomada conociendo que el criterio aplicado de forma consistente sacaria a los 26 no recuperados.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10486,10 +10494,14 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>NOREC: No se consiguio el texto completo. NO falla ningun criterio de §2.2: se excluye por no haberse podido leer. Comprobada su disponibilidad contra Europe PMC, OpenAlex y Semantic Scholar; la unica copia esta en el Zurich Open Repository, es la version ENVIADA --previa a revision por pares-- y el repositorio esta tras una barrera anti-bots. Decision de D. Valdiviezo del 2026-09-02, tomada conociendo que el criterio aplicado de forma consistente sacaria a los 26 no recuperados.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10550,10 +10562,14 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>NOREC: No se consiguio el texto completo. NO falla ningun criterio de §2.2: se excluye por no haberse podido leer. Comprobada su disponibilidad contra Europe PMC, OpenAlex y Semantic Scholar; la unica copia esta en el Zurich Open Repository, es la version ENVIADA --previa a revision por pares-- y el repositorio esta tras una barrera anti-bots. Decision de D. Valdiviezo del 2026-09-02, tomada conociendo que el criterio aplicado de forma consistente sacaria a los 26 no recuperados.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10614,10 +10630,14 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>NOREC: No se consiguio el texto completo. NO falla ningun criterio de §2.2: se excluye por no haberse podido leer. Comprobada su disponibilidad contra Europe PMC, OpenAlex y Semantic Scholar; la unica copia esta en el Zurich Open Repository, es la version ENVIADA --previa a revision por pares-- y el repositorio esta tras una barrera anti-bots. Decision de D. Valdiviezo del 2026-09-02, tomada conociendo que el criterio aplicado de forma consistente sacaria a los 26 no recuperados.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -14878,10 +14898,14 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>REV: Editorial de dos paginas (137-138) firmado por un solo autor. SciELO lo indexa literalmente como «Tipo de literatura: Editorial» y «No citable». Un editorial no aporta datos primarios propios, que es lo que §2.2 exige. El texto no se pudo leer --scielo.sld.cu no resuelve ni desde el canal ni desde el navegador-- asi que la exclusion se apoya en la indexacion del propio repositorio, no en el articulo.</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -725,7 +725,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-02</t>
+          <t>Generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -7098,10 +7098,14 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>ORG: Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT06605651), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7158,10 +7162,14 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>ORG: Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT06605651), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11798,10 +11806,14 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>ORG: Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (CTIS 2022-500541-24-00), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -12306,10 +12318,14 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>ORG: Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT06827041), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -13894,10 +13910,14 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N205" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>ORG: Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT06938867), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -14834,10 +14854,14 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>ORG: Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT00937274), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -15154,10 +15178,14 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N225" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>ORG: Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT05277350), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -15214,10 +15242,14 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N226" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>OFF: No evalua fagoterapia en pacientes (encuesta, epidemiologia, prensa, otra terapia). Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT05618418), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -15342,10 +15374,14 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N228" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>OFF: No evalua fagoterapia en pacientes (encuesta, epidemiologia, prensa, otra terapia). Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT05314426), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -15522,10 +15558,14 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N231" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>ORG: Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT05967130), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -15646,10 +15686,14 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N233" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>ORG: Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT07076238), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -8326,10 +8326,14 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>NOORG: La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra. Ficha completa de ClinicalTrials.gov NCT06185920, bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo. Comprobado sobre la ficha entera: «Pseudomonas» y «aeruginosa» no aparecen en NINGUN campo del registro.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11934,10 +11938,14 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>NOORG: La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra. Ficha completa de ClinicalTrials.gov NCT04682964, bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo. La ficha SI nombra a P. aeruginosa, pero en el campo «briefSummary» y dentro del espectro litico declarado del preparado de fagos, no como la bacteria de los pacientes: los criterios de elegibilidad no exigen ningun organismo.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -12194,10 +12202,14 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>NOORG: La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra. Ficha completa de ClinicalTrials.gov NCT05537519, bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo. Comprobado sobre la ficha entera: «Pseudomonas» y «aeruginosa» no aparecen en NINGUN campo del registro.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -14414,10 +14426,14 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N213" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>NOORG: La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra. Ficha completa de ClinicalTrials.gov NCT04325685, bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo. Comprobado sobre la ficha entera: «Pseudomonas» y «aeruginosa» no aparecen en NINGUN campo del registro.</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -14478,10 +14494,14 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>NOORG: La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra. Ficha completa de ClinicalTrials.gov NCT04325685, bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo. Comprobado sobre la ficha entera: «Pseudomonas» y «aeruginosa» no aparecen en NINGUN campo del registro.</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -14794,10 +14814,14 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N219" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>NOORG: La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra. Ficha completa de ClinicalTrials.gov NCT00663091, bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo. La ficha SI nombra a P. aeruginosa, pero en el campo «description» y dentro del espectro litico declarado del preparado de fagos, no como la bacteria de los pacientes: los criterios de elegibilidad no exigen ningun organismo.</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -15118,10 +15142,14 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N224" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>NOORG: La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra. Ficha completa de ClinicalTrials.gov NCT04724603, bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo. Comprobado sobre la ficha entera: «Pseudomonas» y «aeruginosa» no aparecen en NINGUN campo del registro.</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -15438,10 +15466,14 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N229" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>NOORG: La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra. Ficha completa de ClinicalTrials.gov NCT04650607, bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo. Comprobado sobre la ficha entera: «Pseudomonas» y «aeruginosa» no aparecen en NINGUN campo del registro.</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -725,7 +725,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-14</t>
+          <t>Generado el 2026-09-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -725,7 +725,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-15</t>
+          <t>Generado el 2026-09-16</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -725,7 +725,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-16</t>
+          <t>Generado el 2026-09-22</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -6522,10 +6522,14 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>PRO: Protocolo de ensayo sin resultados. Estructura de protocolo de BMJ Open (INTRODUCTION / METHODS AND ANALYSIS / Ethics and dissemination) y 71 apariciones de «will be», el mismo criterio con que se excluyeron EST-035, EST-052, EST-083 y EST-122. La nota firmada del dominio D5 ya lo decia: «Es un protocolo; aun no hay resultados.» Firmado por los dos revisores el 2026-09-22.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -725,7 +725,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-22</t>
+          <t>Generado el 2026-09-23</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -725,7 +725,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-23</t>
+          <t>Generado el 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -2034,10 +2034,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>ORG: Ningún paciente con P. aeruginosa tratado con fagos. No contiene pseudomona. Lectura firmada del 2026-09-30: declarada no verificable / no aplica: en el paciente no se aisló P. aeruginosa (Staphylococcus, Enterococcus, Streptococcus); P. aeruginosa solo aparece en la composición de los productos Eliava. No hay antibiograma.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5946,10 +5950,14 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>ORG: Ningún paciente con P. aeruginosa tratado con fagos. No contiene pseudomona. Lectura firmada del 2026-09-30: no aplica / declarada no verificable: entre los patógenos aislados (Tabla 2: E. coli, K. pneumoniae, P. mirabilis, S. epidermidis, S. aureus) no hay P. aeruginosa; P. aeruginosa solo figura en la composición del producto Sextaphage. La resistencia «MDR» se describe de forma agregada para todo el estudio.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -13866,10 +13874,14 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>ORG: Ningún paciente con P. aeruginosa tratado con fagos. No contiene pseudomona. Lectura firmada del 2026-09-30: no aplica: el estudio solo incluye infecciones protésicas de cadera por Staphylococcus spp. (la etiología no estafilocócica es criterio de exclusión); no hay pacientes con P. aeruginosa ni clase de resistencia de esa especie.</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -15086,10 +15098,14 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>ORG: Ningún paciente con P. aeruginosa tratado con fagos. No contiene pseudomona. Lectura firmada del 2026-09-30: no aplica: infección de LVAD por Staphylococcus aureus sensible a meticilina; P. aeruginosa solo aparece en la discusión como referencia a otros estudios, no en este paciente.</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -725,7 +725,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-03</t>
+          <t>Generado el 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4978,10 +4978,14 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>NOREC: Idioma no verificable sobre el artículo: solo se probó el resumen en inglés, en una revista que no publica de forma nativa en inglés. Resumen en inglés (1 161 caracteres). DOI 10.20953/1729-9225-2017-4-49-54 → ficha inglesa del editor (phdynasty.ru/en/), que no enlaza el artículo ni declara su idioma. Sin texto completo: no es acceso abierto. SIN TEXTO COMPLETO</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6270,10 +6274,14 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>NOREC: Idioma no verificable sobre el artículo: solo se probó el resumen en inglés, en una revista que no publica de forma nativa en inglés. Resumen en inglés (1 337 caracteres). DOI 10.20953/1729-9225-2017-1-35-40 → ficha inglesa del editor, sin enlace al artículo. Zenodo 1997795 guarda un .docx de 17 756 bytes, que no se ha descargado. SIN TEXTO COMPLETO</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11318,10 +11326,14 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>ORG: Sin subgrupo separable de P. aeruginosa. La frase es la composición del cóctel empírico que se aplicó hasta tener el fago personalizado (p. 2). El artículo no dice cuántos pacientes tenían P. aeruginosa ni desglosa por organismo, y el criterio de población exige un subgrupo separable. Si sale: deja de ser uno de los 4 con grupo de comparación y sus juicios RoB 2 salen de la Tabla 7. no separa pacientes con Pseudomonas</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11382,10 +11394,14 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>ORG: Sin subgrupo separable de P. aeruginosa. La frase es la composición del cóctel empírico que se aplicó hasta tener el fago personalizado (p. 2). El artículo no dice cuántos pacientes tenían P. aeruginosa ni desglosa por organismo, y el criterio de población exige un subgrupo separable. Si sale: deja de ser uno de los 4 con grupo de comparación y sus juicios RoB 2 salen de la Tabla 7. no separa pacientes con Pseudomonas</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -13674,10 +13690,14 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N201" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>NOREC: Idioma no verificable sobre el artículo: solo se probó el resumen en inglés, en una revista que no publica de forma nativa en inglés. Resumen en inglés (1 994 caracteres). Sin DOI ni otro identificador consultable; nunca se comprobó más allá del resumen. SIN TEXTO COMPLETO</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -725,7 +725,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-06</t>
+          <t>Generado el 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -1146,10 +1146,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2618,10 +2622,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2994,10 +3002,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3058,10 +3070,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3118,10 +3134,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3246,10 +3266,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3306,10 +3330,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3370,10 +3398,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3430,10 +3462,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3558,10 +3594,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3622,10 +3662,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3686,10 +3730,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3746,10 +3794,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3810,10 +3862,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4002,10 +4058,14 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4066,10 +4126,14 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4394,10 +4458,14 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5890,10 +5958,14 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6022,10 +6094,14 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6082,10 +6158,14 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6606,10 +6686,14 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6674,10 +6758,14 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6738,10 +6826,14 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6798,10 +6890,14 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6862,10 +6958,14 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6926,10 +7026,14 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7054,10 +7158,14 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7250,10 +7358,14 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7578,10 +7690,14 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como resumen de congreso. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7706,10 +7822,14 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7766,10 +7886,14 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7830,10 +7954,14 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8026,10 +8154,14 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8086,10 +8218,14 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8874,10 +9010,14 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8934,10 +9074,14 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8998,10 +9142,14 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9062,10 +9210,14 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9262,10 +9414,14 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9394,10 +9550,14 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9582,10 +9742,14 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9770,10 +9934,14 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9834,10 +10002,14 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9894,10 +10066,14 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9954,10 +10130,14 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10018,10 +10198,14 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10078,10 +10262,14 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10138,10 +10326,14 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10202,10 +10394,14 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10730,10 +10926,14 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -11462,10 +11662,14 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como resumen de congreso. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11718,10 +11922,14 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11778,10 +11986,14 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11906,10 +12118,14 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -12034,10 +12250,14 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -12298,10 +12518,14 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -12486,10 +12710,14 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -12550,10 +12778,14 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -12610,10 +12842,14 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -12674,10 +12910,14 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -12738,10 +12978,14 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12802,10 +13046,14 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -12862,10 +13110,14 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N188" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -12994,10 +13246,14 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -13054,10 +13310,14 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N191" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -13118,10 +13378,14 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N192" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -13246,10 +13510,14 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13310,10 +13578,14 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>NOPDF: Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -13502,10 +13774,14 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -13562,10 +13838,14 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -13626,10 +13906,14 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -14154,10 +14438,14 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -14214,10 +14502,14 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N209" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -14278,10 +14570,14 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como resumen de congreso. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -14342,10 +14638,14 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N211" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -14402,10 +14702,14 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N212" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -14666,10 +14970,14 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N216" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -14726,10 +15034,14 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N217" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -14790,10 +15102,14 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -15570,10 +15886,14 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N230" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -15698,10 +16018,14 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>incluido</t>
-        </is>
-      </c>
-      <c r="N232" t="inlineStr"/>
+          <t>excluido después</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>NOPDF: Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -725,7 +725,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-07</t>
+          <t>Generado el 2026-10-08</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -725,7 +725,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-08</t>
+          <t>Generado el 2026-10-12</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -89,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,11 +104,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -521,211 +528,218 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Las secciones y tablas que se citan son las del informe extendido (manuscrito maestro). En el manuscrito preparado para la revista las secciones no van numeradas.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Cuántas filas</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>233 filas de datos</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Qué significa cada columna</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Identificador del informe</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>columna interna: record_id</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>columna interna: estudio</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Idioma declarado</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>columna interna: idioma_declarado</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>De dónde sale el idioma declarado</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>columna interna: fuente_declarado</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Idioma del texto</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>columna interna: idioma_del_texto</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Clase de evidencia</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>columna interna: clase_de_evidencia</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Prueba</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>columna interna: prueba</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>columna interna: estado</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Caracteres del resumen</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>columna interna: caracteres_de_resumen</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Título alternativo</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>columna interna: titulo_alternativo</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Revista</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>columna interna: revista</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>columna interna: titulo</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>¿Quedó incluido al final?</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>columna interna: estado_final</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Por qué se excluyó</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>columna interna: motivo_de_la_exclusion</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Generado el 2026-10-12</t>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Generado el 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -760,72 +774,72 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Identificador del informe</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Idioma declarado</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>De dónde sale el idioma declarado</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Idioma del texto</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Clase de evidencia</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Prueba</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Caracteres del resumen</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Título alternativo</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Revista</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>¿Quedó incluido al final?</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>Por qué se excluyó</t>
         </is>

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -739,7 +739,7 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-14</t>
+          <t>Generado el 2026-10-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -739,7 +739,7 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-15</t>
+          <t>Generado el 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
+++ b/verificables revisión sistemática/S9_idioma_por_informe_y_clase_de_evidencia.xlsx
@@ -739,7 +739,7 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-19</t>
+          <t>Generado el 2026-10-20</t>
         </is>
       </c>
     </row>
